--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -20612,7 +20612,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Registrations grid lists records (50 rows on page 1 of 1,263,207 total); registration #135995233909 present with its details on the row.</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20633,7 +20643,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Opening a record routes to the record shell /registration/51af05dc-a584-4076-9453-e2e825f72e93; default tab is Details.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20660,7 +20680,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Tabs displayed: ['Details', 'Customer Details', 'Claim', 'Registration Survey', 'Communication', 'Device Diagnostics', 'Product Review', 'Timeline', 'Notes']. All expected tabs present; additional undocumented tab(s): ['Device Diagnostics'].</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20680,7 +20710,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Details tab renders registration details — fields found: ['Device', 'Device Category', 'Serial Number', 'Registration Number', 'Plan', 'Coverage Amount', 'Batch Number'].</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20702,7 +20742,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Customer Details' tab is clickable and renders its panel (grid/rows present=True; panel heading 'CUSTOMER DETAILS' shown).</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20773,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Claim' tab is clickable and renders its panel (grid/rows present=True; panel heading 'CLAIM' shown).</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20744,7 +20804,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Registration Survey' tab is clickable and renders its panel (grid/rows present=True; panel heading 'REGISTRATION SURVEY' shown).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20765,7 +20835,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Communication' tab is clickable and renders its panel (grid/rows present=True; panel heading 'COMMUNICATION' shown).</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20786,7 +20866,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Product Review' tab is clickable and renders its panel (grid/rows present=True; panel heading 'PRODUCT REVIEW' shown).</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20807,7 +20897,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Timeline' tab is clickable and renders its panel (grid/rows present=True; panel heading 'TIMELINE' shown).</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20828,7 +20928,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Notes' tab is clickable and renders its panel (grid/rows present=True; panel heading 'NOTES' shown).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20880,7 +20990,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Registration details section displays: ['Device', 'Device Category', 'Serial Number', 'Identifier for Vendor', 'App Version', 'Device Name'].</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20903,7 +21023,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product details section displays: ['Product Barcode', 'Product', 'Plan', 'Coverage Amount', 'Batch Number'].</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20929,7 +21059,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store Receipt section displays with Store/Branch/Receipt Number fields and receipt actions: {'store': True, 'branch': True, 'num': True, 'view': True, 'replace': True}.</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20949,7 +21089,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store, Branch and Receipt Number accept keyboard input ({'branch': True, 'receipt_number': True}). Values were reverted and NOT saved — live environment, real customer record.</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20970,7 +21120,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>View Receipt opens a modal displaying the uploaded receipt image ({'img': True, 'txt': 'Registration Details\nNavigate\nBrowse\nRegistrations\n135995233909\nRegistration: 13'}).</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -20990,7 +21150,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No replace-file control exists on this build. The Store Receipt section offers only view actions (View Receipt / View Image / View Photo) and there is no file input anywhere in the Details tab or the View Receipt modal (input[type=file] count = 0 in both). Test case expects a replace-file button that opens the OS file explorer.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>DEF-REG-02</t>
         </is>
       </c>
     </row>
@@ -21011,7 +21181,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Cannot be executed: the prerequisite replace-file control does not exist (see Details|6 / DEF-REG-02). Independently, replacing a receipt would overwrite a real customer stored image on a live production-data environment.</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21031,7 +21211,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>View Receipt renders the stored receipt for inspection (pages open=2).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21064,10 +21254,19 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
-        </is>
-      </c>
-      <c r="F23" s="68" t="n"/>
+          <t>Customer details populate on the fields (11 of 17 fields carry values; fields: ['pin', 'batch_number', 'coverage_amount', 'country_lu', 'language', 'first_name', 'last_name', 'email', 'phone_code', 'mobile_phone', 'street', 'unit_number']).</t>
+        </is>
+      </c>
+      <c r="F23" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="14.25" customHeight="1" s="41">
       <c r="B24" s="58" t="n">
@@ -21085,7 +21284,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>14 of 17 customer fields are editable (not disabled/read-only).</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21106,7 +21315,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Customer field 'first_name' accepts an updated value and reflects it on the field ({'ok': True, 'id': 'first_name', 'old': 'Joseph', 'reverted': True}). Reverted immediately and NOT saved — real customer record on a live environment.</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21139,7 +21358,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t xml:space="preserve">New opens the New Claim Report modal. Heading/first fields: New Claim Report | close | 1 | 2 | 3 | Step 1 | Product Details | Pin | Plan * | Device * | Serial Number * | system_update | Product Barcode | 810135819299 | Product Name | Simple Tempered </t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21163,7 +21392,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Step 1 displays product details — ['Pin', 'Plan', 'Device', 'Serial', 'Barcode', 'Product'] shown.</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21183,7 +21422,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next advances the wizard to Step 2 (clicked 'chevron_rightNext').</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21213,7 +21462,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Step 2 displays customer details — ['Email', 'First Name', 'Last Name', 'Phone', 'Address'] shown.</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21492,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Notes is NOT enforced. On Step 2 the field is labelled "Notes *" and the textarea #notes carries required=true, yet with it empty the wizard advanced from Step 2 to Step 3 and surfaced no validation message. Expected: the Notes field validates and the user cannot proceed to the next step.</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>DEF-REG-01</t>
         </is>
       </c>
     </row>
@@ -21253,7 +21522,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Notes field (#notes) accepts typed input — reads 'Regression QA verification note — wizard validated, no claim'.</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21273,7 +21552,17 @@
       </c>
       <c r="E33" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next advances the wizard from Step 2 to Step 3 (clicked) — Step 3 is the Claim Receipt / review step.</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21295,7 +21584,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Customer Information section shows ['Name', 'Phone', 'Email', 'Address'].</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21317,7 +21616,17 @@
       </c>
       <c r="E35" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage Information section shows ['Coverage Amount', 'Coverage Type', 'Coverage'].</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21337,7 +21646,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device/Product Guarantee Information section shows ['Covered Product', 'Guarantee', 'Product'].</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21360,7 +21679,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed by choice: Done commits a real claim report against live customer registration #031792542792 on an environment carrying production data. Wizard verified end-to-end through the review step, then cancelled.</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21382,7 +21711,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed by choice: this step emails the customer at their real address. Suppressed so a regression run cannot contact a real customer. A self-owned registration is not creatable here (Customers has no New; portal-created users are absent from the wizard's customer pool).</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21415,7 +21754,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21435,7 +21784,17 @@
       </c>
       <c r="E41" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input and reflects 'RegressionTest Note Aug17' (True).</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21455,7 +21814,17 @@
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21476,7 +21845,17 @@
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the notes grid (found=True).</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21497,7 +21876,17 @@
       </c>
       <c r="E44" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal with existing details populated — Title reads 'RegressionTest Note Aug17', content reads 'Regression test note created by automated QA run 2026-08-17. Safe to d'.</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21518,7 +21907,17 @@
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edited title reflects on the field as 'RegressionTest Note Aug17 [edited]' (True).</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -21539,7 +21938,17 @@
       </c>
       <c r="E46" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note title persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -24616,7 +24616,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Repair shops grid displays with its columns and data (1 shop row(s); columns []). Note: this environment holds only the one shop record.</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24636,7 +24646,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Repair Shops' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24657,7 +24677,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Name', 'Status']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24678,7 +24708,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Status'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24699,7 +24739,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dependent dropdown for Status: ['Active']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24721,7 +24771,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Active' reflects on the field and the Add Filter button becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24801,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24831,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (0 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24861,19 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present; download not captured headless: Locator.click: Timeout 30000ms exceeded.
+Call log:
+  - waiti</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24906,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Repair Shop modal: New Repair Shop | close | Upload | file_upload | Name * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24834,7 +24936,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (1); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24854,7 +24966,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the profile image section.</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24875,7 +24997,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Repair shop name input reflects 'RegressionTest ShopAug17'.</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24896,7 +25028,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the modal and routes to the shop record (/shop/48c20651-cbec-4182-98ba-525fe28a8216).</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24931,7 +25073,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record action buttons displayed: ['Save', 'Save and Close'] (all buttons: ['close', 'format_list_bulleted', 'Navigate', 'Browse', 'Repair Shops', 'RegressionTest ShopAug17', 'keyboard_arrow_left', 'keyboard_arrow_right', 'close', 'checkSave', 'checkSave and Close', 'searchView Image']).</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24954,7 +25106,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Repair shop details display — image present=True, name shown=True.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -24974,7 +25136,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Default opened tab is Branches (tabs: ['Branches', 'Timeline', 'Notes']).</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25007,7 +25179,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch filter control opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25029,7 +25211,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists branch grid columns: ['Branch Name', 'Address', 'Phone', 'Status']</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25242,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Branch Name'; 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25071,7 +25273,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen branch column: ['Active']</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25093,7 +25305,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Active' reflects on the field and applies to the branch grid.</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25113,7 +25335,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies and creates a filtered tab in the branches grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25133,7 +25365,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch search field accepts input and filters the branch grid.</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25153,7 +25395,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present on the branch grid; download not captured headless.</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25174,7 +25426,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Branch modal with its form: New Branch | close | Upload | file_upload | Branch Name * | Operating Hours | Operating Days | × | × | check_box_outline_blank | Open 24 Hours | Phone T</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25194,7 +25456,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch profile image section exposes a file input (1) which opens the file explorer.</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25214,7 +25486,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the branch profile image section.</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25516,17 @@
       </c>
       <c r="E33" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch name input reflects 'RegressionTest BranchAug17'.</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25255,7 +25547,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Operating Days field opens a dropdown: ['Sunday', 'Monday', 'Tuesday', 'Wednesday', 'Thursday', 'Friday', 'Saturday']</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25275,7 +25577,17 @@
       </c>
       <c r="E35" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected operating day 'Sunday' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25296,7 +25608,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>AM (opening) time field opens a dropdown of times: ['6:00 AM', '6:30 AM', '7:00 AM', '7:30 AM', '8:00 AM', '8:30 AM', '9:00 AM', '9:30 AM', '10:00 AM', '10:30 AM', '11:00 AM', '11:30 AM']</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25316,7 +25638,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected AM time '6:00 AM' reflects on the field (field now reads '6:00 AM').</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25337,7 +25669,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>PM (closing) time field opens a dropdown of times: ['5:00 PM', '5:30 PM', '6:00 PM', '6:30 PM', '7:00 PM', '7:30 PM', '8:00 PM', '8:30 PM', '9:00 PM', '9:30 PM', '10:00 PM', '10:30 PM'] …</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25357,7 +25699,17 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected PM time '5:00 PM' reflects on the field (field now reads '5:00 PM').</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25377,7 +25729,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Checking 'Open 24 Hours' (clicked, checked=True) disables the AM and PM time fields — disabled flags before [False, False, False] -&gt; after [False, True, True].</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25397,7 +25759,17 @@
       </c>
       <c r="E41" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone type defaults to 'Work' ({'id': 'undefined-toggle', 'val': 'Workphone'}).</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25789,17 @@
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone type field opens a dropdown listing the alternate option(s): ['Mobile']</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25437,7 +25819,17 @@
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone number input reflects '(415) 555-0123'.</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25457,7 +25849,17 @@
       </c>
       <c r="E44" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Typing an address surfaces suggested result(s) in the autocomplete.</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25477,7 +25879,17 @@
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a suggestion reveals the address breakdown sub-form: ['street', 'city', 'zip_code', 'country', 'state']</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25499,7 +25911,17 @@
       </c>
       <c r="E46" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the branch modal and routes to the branch record (modal still open=False).</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25532,7 +25954,17 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline filter control opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25562,7 +25994,17 @@
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists timeline columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25583,7 +26025,17 @@
       </c>
       <c r="E50" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25604,7 +26056,17 @@
       </c>
       <c r="E51" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on 'Action': ['Create Shop', 'Update Shop']</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25626,7 +26088,17 @@
       </c>
       <c r="E52" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Create Shop' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F52" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25646,7 +26118,17 @@
       </c>
       <c r="E53" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the timeline grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F53" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25666,7 +26148,17 @@
       </c>
       <c r="E54" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline search accepts input and filters the activity list (searching 'Shop' returned: All Activity | arrow_drop_down | Filter Activity | Show all Activity where: | Action | is | Create Shop | Add ).</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25686,7 +26178,17 @@
       </c>
       <c r="E55" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline records the actions performed on this shop — entries found: ['Create Shop', 'Update Shop']. Feed: All Activity | arrow_drop_down | Filter Activity | Show all Activity where: | Action | is | Create Shop | Add Filter | question_answer | August 17, 2026 | Today at 1:39 P</t>
+        </is>
+      </c>
+      <c r="F55" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G55" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25719,7 +26221,17 @@
       </c>
       <c r="E57" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F57" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25739,7 +26251,17 @@
       </c>
       <c r="E58" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F58" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25759,7 +26281,17 @@
       </c>
       <c r="E59" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F59" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25780,7 +26312,17 @@
       </c>
       <c r="E60" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the notes list (found=True).</t>
+        </is>
+      </c>
+      <c r="F60" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25801,7 +26343,17 @@
       </c>
       <c r="E61" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
+        </is>
+      </c>
+      <c r="F61" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G61" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25822,7 +26374,17 @@
       </c>
       <c r="E62" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Change reflects in the title field (True).</t>
+        </is>
+      </c>
+      <c r="F62" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -25843,7 +26405,17 @@
       </c>
       <c r="E63" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F63" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G63" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -26619,7 +26619,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Affiliates grid displays (2 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26649,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Affiliates' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26661,7 +26681,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Affiliate Name', 'Stores', 'Users', 'Actions']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26682,7 +26712,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Affiliate Name'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26703,7 +26743,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dependent dropdown for 'Affiliate Name': ['RegressionTest AffiliateAug17', '{dna:micro}']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26725,7 +26775,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'RegressionTest AffiliateAug17' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26745,7 +26805,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26765,7 +26835,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26785,7 +26865,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Affiliates_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26818,7 +26908,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Affiliate modal: New Affiliate | close | Upload | file_upload | Affiliate Name * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26838,7 +26938,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (1); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26858,7 +26968,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the profile image section.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26879,7 +26999,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Affiliate name input reflects 'RegressionTest AffiliateAug17'.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26901,7 +27031,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the modal and routes to the affiliate record (/affiliate/edccbddb-99af-4fa2-8ccf-d0f98fed9e16).</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26924,7 +27064,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Affiliate record details display — profile image present=True, name shown=True, tabs ['Users', 'Stores', 'Timeline', 'Notes'].</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26957,7 +27107,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Stores' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -26979,7 +27139,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Name', 'Phone', 'Address']</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27000,7 +27170,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Name'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27021,7 +27201,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on 'Name': ['RegressionTest StoreAug17']</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27043,7 +27233,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'RegressionTest StoreAug17' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27063,7 +27263,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27083,7 +27293,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (3 rows matched).</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27103,7 +27323,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Stores_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27123,7 +27353,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Store modal: New Store | close | Upload | file_upload | Name * | Phone Number * | phone | Address * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27143,7 +27383,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store profile image section exposes a file input (1) opening the file explorer.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27163,7 +27413,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the store profile image section.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27183,7 +27443,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store name input reflects 'RegressionTest StoreAug17'.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27203,7 +27473,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store phone number input reflects '(415) 555-0177'.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27223,7 +27503,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Typing an address surfaces suggested result(s) in the autocomplete.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27243,7 +27533,17 @@
       </c>
       <c r="E33" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a suggestion reveals the address breakdown sub-form: ['street', 'city', 'zip_code', 'country', 'state']</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27265,7 +27565,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the store is saved (modal still open=False).</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27298,7 +27608,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline filter control opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27320,7 +27640,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists timeline columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27341,7 +27671,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27362,7 +27702,17 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Dependent value dropdown for 'Action': ['Create Affiliate', 'Create Batch', 'Create Branch', 'Create Employee', 'Create Province', 'Create Registration', 'Create Shop', 'Create Store', 'Create User', 'Update Affiliate']</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27384,7 +27734,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Create Affiliate' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27404,7 +27764,17 @@
       </c>
       <c r="E41" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the timeline (clicked).</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27424,7 +27794,17 @@
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline search accepts input and filters the activity list.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27824,17 @@
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline records actions performed on this affiliate — entries: ['Create Affiliate']. Feed: All Activity | Custom Filter | arrow_drop_down | Filter Activity | Action is Create Affiliate | add_circle | question_answer | August 17, 2026 | Today</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27477,7 +27867,17 @@
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27497,7 +27897,17 @@
       </c>
       <c r="E46" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27517,7 +27927,17 @@
       </c>
       <c r="E47" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27538,7 +27958,17 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the list (found=True).</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27559,7 +27989,17 @@
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27580,7 +28020,17 @@
       </c>
       <c r="E50" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Change reflects in the title field (True).</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -27601,7 +28051,17 @@
       </c>
       <c r="E51" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -26622,12 +26622,12 @@
           <t>Affiliates grid displays (2 rows; columns rendered).</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26652,12 +26652,12 @@
           <t>'Filter Affiliates' opens the filter panel with a 'Select a filter' field.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26684,12 +26684,12 @@
           <t>Filter-field dropdown lists the grid columns: ['Affiliate Name', 'Stores', 'Users', 'Actions']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26715,12 +26715,12 @@
           <t>Selected 'Affiliate Name'; it reflects on the field and 'Select a value' appears.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26746,12 +26746,12 @@
           <t>'Select a value' opens a dependent dropdown for 'Affiliate Name': ['RegressionTest AffiliateAug17', '{dna:micro}']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26778,12 +26778,12 @@
           <t>Value 'RegressionTest AffiliateAug17' selected and reflects on the field; Add Filter becomes available.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26808,12 +26808,12 @@
           <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26838,12 +26838,12 @@
           <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26868,12 +26868,12 @@
           <t>Export downloads 'Affiliates_08-17-2026.csv'.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26911,12 +26911,12 @@
           <t>New opens the New Affiliate modal: New Affiliate | close | Upload | file_upload | Affiliate Name * | close | Cancel | check | Save &amp; Continue</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26941,12 +26941,12 @@
           <t>Profile image section exposes a file input (1); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -26971,12 +26971,12 @@
           <t>Selected image reflects in the profile image section.</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27002,12 +27002,12 @@
           <t>Affiliate name input reflects 'RegressionTest AffiliateAug17'.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27034,12 +27034,12 @@
           <t>Save &amp; Continue ('checkSave &amp; Continue') closes the modal and routes to the affiliate record (/affiliate/edccbddb-99af-4fa2-8ccf-d0f98fed9e16).</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27067,12 +27067,12 @@
           <t>Affiliate record details display — profile image present=True, name shown=True, tabs ['Users', 'Stores', 'Timeline', 'Notes'].</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27110,12 +27110,12 @@
           <t>'Filter Stores' opens the filter panel with a 'Select a filter' field.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27142,12 +27142,12 @@
           <t>Filter-field dropdown lists the grid columns: ['Name', 'Phone', 'Address']</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27173,12 +27173,12 @@
           <t>Selected 'Name'; it reflects on the field and 'Select a value' appears.</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27204,12 +27204,12 @@
           <t>'Select a value' opens a dropdown dependent on 'Name': ['RegressionTest StoreAug17']</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27236,12 +27236,12 @@
           <t>Selected value 'RegressionTest StoreAug17' reflects on the field.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27266,12 +27266,12 @@
           <t>Add Filter applies and creates a filtered tab in the grid (clicked).</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27296,12 +27296,12 @@
           <t>Search field accepts input and filters the grid (3 rows matched).</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27326,12 +27326,12 @@
           <t>Export downloads 'Stores_08-17-2026.csv'.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27356,12 +27356,12 @@
           <t>New opens the New Store modal: New Store | close | Upload | file_upload | Name * | Phone Number * | phone | Address * | close | Cancel | check | Save &amp; Close</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27386,12 +27386,12 @@
           <t>Store profile image section exposes a file input (1) opening the file explorer.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27416,12 +27416,12 @@
           <t>Selected image reflects in the store profile image section.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27446,12 +27446,12 @@
           <t>Store name input reflects 'RegressionTest StoreAug17'.</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27476,12 +27476,12 @@
           <t>Store phone number input reflects '(415) 555-0177'.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27506,12 +27506,12 @@
           <t>Typing an address surfaces suggested result(s) in the autocomplete.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27536,12 +27536,12 @@
           <t>Selecting a suggestion reveals the address breakdown sub-form: ['street', 'city', 'zip_code', 'country', 'state']</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27568,12 +27568,12 @@
           <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the store is saved (modal still open=False).</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27611,12 +27611,12 @@
           <t>Timeline filter control opens the filter panel.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27643,12 +27643,12 @@
           <t>Filter-field dropdown lists timeline columns: ['Date', 'Action']</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27674,12 +27674,12 @@
           <t>Selected 'Action'; 'Select a value' appears.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27705,12 +27705,12 @@
           <t>Dependent value dropdown for 'Action': ['Create Affiliate', 'Create Batch', 'Create Branch', 'Create Employee', 'Create Province', 'Create Registration', 'Create Shop', 'Create Store', 'Create User', 'Update Affiliate']</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27737,12 +27737,12 @@
           <t>Selected value 'Create Affiliate' reflects on the field.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27767,12 +27767,12 @@
           <t>Add Filter applies to the timeline (clicked).</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27797,12 +27797,12 @@
           <t>Timeline search accepts input and filters the activity list.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27827,12 +27827,12 @@
           <t>Timeline records actions performed on this affiliate — entries: ['Create Affiliate']. Feed: All Activity | Custom Filter | arrow_drop_down | Filter Activity | Action is Create Affiliate | add_circle | question_answer | August 17, 2026 | Today</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27870,12 +27870,12 @@
           <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27900,12 +27900,12 @@
           <t>Title field accepts input (True).</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27930,12 +27930,12 @@
           <t>Message/content rich-text box accepts input (True).</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27961,12 +27961,12 @@
           <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the list (found=True).</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -27992,12 +27992,12 @@
           <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -28023,12 +28023,12 @@
           <t>Change reflects in the title field (True).</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -28054,12 +28054,12 @@
           <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -28254,12 +28254,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>New opens the New Claim modal on Step 1 'Search Registration': New Claim | close | 1 | 2 | 3 | 4 | Step 1  | Search Registration | 	 | IMEI/Serial Number | arrow_upward | 	 | Contract Number | arrow_upward | 	 | Registration Number | arrow_upwar</t>
         </is>
       </c>
       <c r="F2" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28279,12 +28284,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Step 1 grid lists registrations available to claim against (10 rows; columns []).</t>
         </is>
       </c>
       <c r="F3" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28304,12 +28314,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Registration search inside the wizard filters the grid (10 rows matched).</t>
         </is>
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28330,12 +28345,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Selecting a registration row marks its radio and enables the Next button (Next disabled before=True -&gt; enabled after=True).</t>
         </is>
       </c>
       <c r="F5" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28356,12 +28376,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>After selecting a registration, Next moves the flow on to Step 2 Product Details. Sections rendered: ['Step 1 Search Registration', 'Step 2Product Details', 'Step 3Customer Details', 'Step 4Claim Receipt'].</t>
         </is>
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28387,12 +28412,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Step 2 Product Details content: ['Pin', 'Plan', 'Device', 'Product Barcode', 'Serial', 'Product'] — Step 2 | Product Details | Pin | Plan * | Device * | Serial Number * | system_update | Product Barcode | 810135819299 | Product Name | Simple Tempered</t>
         </is>
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28412,12 +28442,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Step 3 Customer Details section is reachable (present).</t>
         </is>
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28452,12 +28487,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Step 3 Customer Details content: ['Email', 'First Name', 'Last Name', 'Phone', 'Address', 'Name'] — Step 3 | Customer Details | Email Address * | email | First Name * | person | Last Name * | person | Phone Number * | Country * | United States | Lang</t>
         </is>
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28477,12 +28517,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Customer details on Step 3 are updatable — editable inputs found: ['email', 'first_name', 'last_name', 'phone_number', 'street', 'unit_number', 'city', 'zip_code', 'textarea', 'notes'].</t>
         </is>
       </c>
       <c r="F10" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28502,12 +28547,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Step 4 section is reachable (Step 4Claim Receipt).</t>
         </is>
       </c>
       <c r="F11" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28532,12 +28582,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Step 4 of the New Claim flow is "Claim Receipt" (an InstaProtek Product Guarantee Claim summary showing Claim Number, Policy Number, Customer Information, Coverage Information, Shipping/Order Details), not the "Problem Summary" the test case describes. No Problem Date or Problem Summary fields exist anywhere in the flow.</t>
         </is>
       </c>
       <c r="F12" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>DEF-CLAIM-03</t>
         </is>
       </c>
     </row>
@@ -28558,12 +28613,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No input fields are rendered on Step 4 — the Claim Receipt step is a read-only summary. Consequence of the Step 4 redesign recorded in Claim Reports|11; there are no Problem Summary fields to type into.</t>
         </is>
       </c>
       <c r="F13" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>DEF-CLAIM-03</t>
         </is>
       </c>
     </row>
@@ -28584,12 +28644,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not executed by choice: Done commits a real claim report against a live customer's registration on an environment carrying production data (1.26M registrations, 123k claims). The wizard was verified through all four steps and then cancelled.</t>
         </is>
       </c>
       <c r="F14" s="40" t="inlineStr">
         <is>
-          <t>Claim filing is app-only - excluded from portal regression.</t>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28623,7 +28688,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Status section displays the claim's progress states: ['Processing', 'Submitted'].</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28647,7 +28722,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Claim section displays the date in the circle plus Claim Number and Date &amp; Time of Claim ({'claimNo': True, 'dt': True, 'circle': True}).</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28667,7 +28752,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Registration is the default tab (tab order: ['Registration', 'Customer Details', 'Location', 'Appointment', 'Claim Receipt', 'Repair Receipt', 'Repair Approval', 'Reimbursement Review', 'Payment Info', 'Timeline', 'Notes']).</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28687,7 +28782,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Customer Details' tab routes to its panel (First Name * | person | Last Name * | person | Email Address * | email | Country Code * | ).</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28707,7 +28812,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Location' tab routes to its panel (Customer Preference | Repair Shop | Address | Keyboard shortcuts | Map data ©2026 Google |).</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28842,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Appointment' tab routes to its panel (No appointment details to show.).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28747,7 +28872,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>There is no "Claim Summary" tab on this build. Tabs present on the claim record: Registration, Customer Details, Location, Appointment, Claim Receipt, Repair Receipt, Repair Approval, Reimbursement Review, Payment Info, Timeline, Notes. The test case expects a Claim Summary tab.</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>DEF-CLAIM-02</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28902,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>There is no "Claim Status Details" tab on this build (same tab list as Record|7). The test case expects a Claim Status Details tab.</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>DEF-CLAIM-02</t>
         </is>
       </c>
     </row>
@@ -28787,7 +28932,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Timeline' tab routes to its panel (All Activity | Custom Filter | arrow_drop_down | Filter Activity | No Results Found!).</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28807,12 +28962,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>'Notes' tab routes to its panel (add | New | All Notes | arrow_drop_down | Filter Notes | 2026 Aug 17 | #79779 | keyboard_a).</t>
         </is>
       </c>
       <c r="F25" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28844,12 +29004,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Registration Number displayed on the Registration tab — ['Registration Number'] present.</t>
         </is>
       </c>
       <c r="F27" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28869,12 +29034,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Plan displayed on the Registration tab — ['Plan'] present.</t>
         </is>
       </c>
       <c r="F28" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28894,12 +29064,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Coverage Amount displayed on the Registration tab — ['Coverage Amount'] present.</t>
         </is>
       </c>
       <c r="F29" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28936,12 +29111,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Device details displayed — ['Device Category', 'Identifier for Vendor', 'Device Name', 'Serial Number', 'Device'].</t>
         </is>
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28961,12 +29141,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Terms and Conditions link present and clickable ({'n': 3, 'tag': 'SPAN', 'href': None}).</t>
         </is>
       </c>
       <c r="F31" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -28989,12 +29174,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Product Details displayed — ['Product Barcode', 'Product Name', 'Product'].</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29017,12 +29207,17 @@
       </c>
       <c r="E33" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Store Receipt section displayed — ['Store Receipt', 'View Receipt', 'Receipt'].</t>
         </is>
       </c>
       <c r="F33" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29042,12 +29237,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Store field on the claim's Registration tab: {'id': 'store_id-select', 'dis': False, 'ro': False}</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29067,12 +29267,17 @@
       </c>
       <c r="E35" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Store field accepts input (store_id-select). Value reverted and NOT saved — live customer claim.</t>
         </is>
       </c>
       <c r="F35" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29092,12 +29297,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Branch field displayed on the Registration tab ({'present': True, 'dis': False, 'ro': False, 'vis': True, 'val': ''}).</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29117,12 +29327,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Branch accepts typed input and reflects it (True). Value reverted and NOT saved — live customer claim record.</t>
         </is>
       </c>
       <c r="F37" s="40" t="inlineStr">
         <is>
-          <t>BLOCKED - prerequisite: create a claim-eligible registration first (test barcode 810135810326 + mock data in READ ME), then file the claim in the app (filing is app-only), which opens the claim record in the portal, then run. Delete the test record after.</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29142,7 +29357,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Receipt Number field displayed on the Registration tab ({'present': True, 'dis': False, 'ro': False, 'vis': True, 'val': ''}).</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29162,7 +29387,17 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Receipt Number accepts typed input and reflects it (True). Value reverted and NOT saved — live customer claim record.</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29182,7 +29417,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>View Receipt control present and actionable (SPAN).</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29227,7 +29472,17 @@
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Customer details displayed on the tab — ['First Name', 'Last Name', 'Email', 'Phone', 'Address', 'Country'].</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29260,7 +29515,17 @@
       </c>
       <c r="E44" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Appointment Date field present and selectable (['date']).</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29281,7 +29546,17 @@
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No Appointment Time field is rendered for this claim's current stage. Panel shows: No appointment details to show.. Not forced — live customer claim.</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29313,7 +29588,17 @@
       </c>
       <c r="E47" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Order Date displayed — ['Order Date', 'Date']. Panel: Warranty Replacement Confirmation | Order Date |  | 08/17/2026 |  | Claim Number |  | 1787000371907 |  | Shipping Details: |  | Dan Holub |  | dan</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29333,7 +29618,17 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Claim Number displayed — ['Claim Number']. Panel: Warranty Replacement Confirmation | Order Date |  | 08/17/2026 |  | Claim Number |  | 1787000371907 |  | Shipping Details: |  | Dan Holub |  | dan</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29357,7 +29652,17 @@
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Shipping details displayed — ['Shipping']. Panel: Warranty Replacement Confirmation | Order Date |  | 08/17/2026 |  | Claim Number |  | 1787000371907 |  | Shipping Details: |  | Dan Holub |  | dan</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29382,7 +29687,17 @@
       </c>
       <c r="E50" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Order Details displayed — ['Order Details', 'Order']. Panel: Warranty Replacement Confirmation | Order Date |  | 08/17/2026 |  | Claim Number |  | 1787000371907 |  | Shipping Details: |  | Dan Holub |  | dan</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29404,7 +29719,17 @@
       </c>
       <c r="E51" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Support information section displayed — ['support', 'Phone', 'Email']. Panel: Warranty Replacement Confirmation | Order Date |  | 08/17/2026 |  | Claim Number |  | 1787000371907 |  | Shipping Details: |  | Dan Holub |  | dan</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29436,7 +29761,17 @@
       </c>
       <c r="E53" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device Insurance Details section displays the insurance question (1 checkbox(es) present). Panel: Device Insurance Details | check_box_outline_blank | Is the customer using an insurance? | Receipt Details | Date (MM/DD/YYYY) *</t>
+        </is>
+      </c>
+      <c r="F53" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29457,7 +29792,17 @@
       </c>
       <c r="E54" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The insurance question can be checked (checked=True); doing so reveals the insurance field.</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29822,17 @@
       </c>
       <c r="E55" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device Insurance field opens its options list: ['Asurion', 'Assurant', 'Apple Care', 'Samsung Care']</t>
+        </is>
+      </c>
+      <c r="F55" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G55" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29497,7 +29852,17 @@
       </c>
       <c r="E56" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected insurance option 'Asurion' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F56" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29521,7 +29886,17 @@
       </c>
       <c r="E57" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Receipt Details section displays — ['Date', 'Amount', 'Covered', 'Receipt Details'] (fields: ['number', 'date', 'is_customer_using_insurance', 'device_insurance', 'repair_amount', 'phone_name-select', 'covered_amount']).</t>
+        </is>
+      </c>
+      <c r="F57" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29542,7 +29917,17 @@
       </c>
       <c r="E58" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Date field present and selectable in Receipt Details ({'id': 'date', 'ph': ''}).</t>
+        </is>
+      </c>
+      <c r="F58" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29563,7 +29948,17 @@
       </c>
       <c r="E59" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Amount field accepts input — field now reads 'USD  123.45'. Value reverted, nothing saved.</t>
+        </is>
+      </c>
+      <c r="F59" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29584,7 +29979,17 @@
       </c>
       <c r="E60" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>A device selector is available in Receipt Details (2 select(s) rendered).</t>
+        </is>
+      </c>
+      <c r="F60" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29605,7 +30010,17 @@
       </c>
       <c r="E61" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Covered amount field does not accept input. #covered_amount is a plain text input with disabled=false, readOnly=false and no maxlength/pattern, yet it stays at "USD  0.00" under every input method tried: Playwright fill(), select-all + retype, and character-by-character keyboard entry. The adjacent #repair_amount field, which is rendered identically, accepts input normally (typing 250 gives "USD  2.50"). Expected: user can input a covered amount and it reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F61" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G61" s="40" t="inlineStr">
+        <is>
+          <t>DEF-CLAIM-01</t>
         </is>
       </c>
     </row>
@@ -29626,7 +30041,17 @@
       </c>
       <c r="E62" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>An image upload control is available in Receipt Details (1 file input(s)); it opens the OS file explorer. Upload not committed — live customer claim.</t>
+        </is>
+      </c>
+      <c r="F62" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29658,7 +30083,17 @@
       </c>
       <c r="E64" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F64" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G64" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29678,7 +30113,17 @@
       </c>
       <c r="E65" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F65" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G65" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29698,7 +30143,17 @@
       </c>
       <c r="E66" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F66" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G66" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29719,7 +30174,17 @@
       </c>
       <c r="E67" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the list (found=True).</t>
+        </is>
+      </c>
+      <c r="F67" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G67" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29740,7 +30205,17 @@
       </c>
       <c r="E68" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
+        </is>
+      </c>
+      <c r="F68" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G68" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29761,7 +30236,17 @@
       </c>
       <c r="E69" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Change reflects in the title field (True).</t>
+        </is>
+      </c>
+      <c r="F69" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G69" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -29782,7 +30267,17 @@
       </c>
       <c r="E70" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F70" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G70" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -16218,7 +16218,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage types grid displays (11 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16238,7 +16248,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Coverage Types' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16259,7 +16279,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Coverage Type', 'Created']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16310,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Coverage Type'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16301,7 +16341,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dependent dropdown for 'Coverage Type': ['Camera Repair Guarantee', 'Case &amp; Screen Protector Guarantee', 'Case Guarantee', 'Device Guarantee Excluding Screen Repair', 'Product Replacement', 'Repair Guarantee', 'Repair Or Replacement', 'Screen Coverage']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16373,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Camera Repair Guarantee' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16403,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16433,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16463,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Coverage_types_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16403,7 +16493,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record/modal (1 row(s) matched 'RegressionTest0817'): Edit Coverage Type Details | close | Coverage Type Name * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16423,7 +16523,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16554,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT'.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16464,7 +16584,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16485,7 +16615,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16658,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Coverage Type modal: New Coverage Type | close | Coverage Type Name * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16539,7 +16689,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage type name accepts input — field 'Coverage Type Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16560,7 +16720,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16862,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage cost types grid displays (5 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16712,7 +16892,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Coverage Cost Types' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16733,7 +16923,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Coverage Cost Type', 'Created']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16954,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Coverage Cost Type'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16775,7 +16985,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dependent dropdown for 'Coverage Cost Type': ['Deductible', 'Repair', 'Repair Or Replacement', 'Replacement', 'Shipping &amp; Handling']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16797,7 +17017,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Deductible' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16817,7 +17047,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16837,7 +17077,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (0 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16857,7 +17107,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Coverage_cost_types_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16877,7 +17137,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record/modal (1 row(s) matched 'RegressionTest0817'): Edit Coverage Cost Type Details | close | Coverage Cost Type * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16897,7 +17167,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16918,7 +17198,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT'.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16938,7 +17228,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16959,7 +17259,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16992,7 +17302,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Coverage Cost Type modal: New Coverage Cost Type | close | Coverage Cost Type * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -17013,7 +17333,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage cost type name accepts input — field 'Coverage Cost Type *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -17034,7 +17364,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -8368,7 +8368,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Repair network grid displays (1 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8398,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Repair Network' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8429,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Repair Network Name']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8460,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Repair Network Name'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8491,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dependent dropdown for 'Repair Network Name': []</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8523,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'None' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8553,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8583,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (0 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8613,19 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present; download not captured headless: Locator.click: Timeout 30000ms exceeded.
+Call log:
+  - waiti</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8645,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record/modal (1 row(s) matched 'RegressionTest0817'): Edit Repair Network Details | close | Repair Network Name * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8675,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8706,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('Save &amp; Continue') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT'.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8736,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8767,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8810,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Repair Network modal: New Repair Network | close | Repair Network Name * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8841,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Repair network name accepts input — field 'Repair Network Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8872,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('Save &amp; Continue') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12688,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Languages grid displays (3 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12718,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Languages' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12557,7 +12749,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Language', 'ISO Code', 'Date Format', 'Time Format']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12780,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t xml:space="preserve">Selecting a filter column on the Languages grid crashes the page. The app throws "TypeError: array[key].filter is not a function at SelectFilter.mapArrayValues" (uncaught at GetLanguageFilter) and the entire page renders blank (document body length 0, no controls); a reload is required to recover. Reproduced on ALL FOUR filter columns (Language, ISO Code, Date Format, Time Format). The identical interaction on other settings grids (e.g. Coverage </t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-01</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12811,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Cannot reach 'Select a value' dropdown: the page has already crashed to a blank screen at the previous step (see Grid|4 / DEF-SET-01).</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12843,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Cannot reach selecting a filter value: the page has already crashed to a blank screen at the previous step (see Grid|4 / DEF-SET-01).</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12641,7 +12873,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Cannot reach the Add Filter button: the page has already crashed to a blank screen at the previous step (see Grid|4 / DEF-SET-01).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12661,7 +12903,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the languages grid (1 row(s) matched 'Eng').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12933,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Languages_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12963,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record (1 row(s) matched 'RegressionTest0817'): Edit Language | close | Upload | file_upload | Language * | ISO Code * | language | Date Format * | yyyy-MM-dd | Time Format | radio_bu</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12721,7 +12993,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12742,7 +13024,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT'.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12762,7 +13054,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12783,7 +13085,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12816,7 +13128,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Language modal: New Language | close | Upload | file_upload | Language * | ISO Code * | language | Date Format * | Time Format | radio_button_unchecked | 12</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12836,7 +13158,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image/upload section exposes a file input (1 present); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12856,7 +13188,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12876,7 +13218,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Language accepts input — field 'Language *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12896,7 +13248,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Iso code accepts input — field 'ISO Code *' now reads 'rt'.</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12916,7 +13278,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Click date format field — 'Date Format *' opened; options: ['yyyy-MM-dd', 'dd/MM/yyyy', 'dd.MM.yyyy', 'd/MM/yyyy', 'dd-MM-yyyy', 'M/d/yyyy']</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12936,7 +13308,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'yyyy-MM-dd' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12956,7 +13338,18 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Select time format — radio 'radio_button_checked
+12 Hours' selected (2 option(s) in the group).</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12977,7 +13370,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13109,7 +13512,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Regions grid displays (4 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13542,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Regions' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13573,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Region Name', 'Currency', 'Currency Code', 'Currency Symbol', 'Decimal Symbol', 'Decimal Digits', 'Digit Grouping Symbol', 'Languages']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13171,7 +13604,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Region Name'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13635,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dependent dropdown for 'Region Name': ['Canada', 'Puerto Rico', 'United Kingdom', 'United States']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13667,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Canada' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13697,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13727,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13757,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Regions_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13787,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a record on the regions grid opens its record — routes to /portal/regions/&lt;id&gt; and renders the full-page Region Details view (header "Region: Canada", Region Name field, Save / Save and Close / Delete actions, Date Created 07/06/2020).</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13817,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Editing the region name was not executed: only the four live production region records exist (no self-created test record is possible — see New Region|4), and regions are live configuration data on an environment carrying production traffic.</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13335,7 +13848,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Saving an edited region was not executed: only the four live production region records exist (no self-created test record is possible — see New Region|4), and regions are live configuration data on an environment carrying production traffic.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13355,7 +13878,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Deleting a region was not executed: only the four live production region records exist (no self-created test record is possible — see New Region|4), and regions are live configuration data on an environment carrying production traffic.</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13909,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Confirming the delete was not executed: only the four live production region records exist (no self-created test record is possible — see New Region|4), and regions are live configuration data on an environment carrying production traffic.</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13952,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Region modal: New Region | close | Upload | file_upload | Region Name * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13982,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image/upload section exposes a file input (1 present); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13449,7 +14012,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13470,7 +14043,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The Region Name field is a dropdown of selectable regions, not a free-text field, and it offers NO options: the four selectable regions (Canada, Puerto Rico, United Kingdom, United States) all already exist as records ['Canada', 'Puerto Rico', 'United Kingdom', 'United States']. A new region therefore cannot be created on this environment. Typing into the field does not set a value and Save is rejected with 'Region Name is required'.</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13491,7 +14074,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Cannot save a new region — no selectable region value is available (see New Region|4).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14497,7 +15090,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Administrators grid displays (4 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14517,7 +15120,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Administrators' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14538,7 +15151,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Company Name']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14559,7 +15182,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Company Name'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14580,7 +15213,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dependent dropdown for 'Company Name': ['InstaProtek (Canada)', 'InstaProtek (Japan)', 'InstaProtek (Warranty)', 'InstaProtek Canada', 'Instaprotek Enterprise', 'InstaProtek(CameraProtection)', 'Instaprotek(Device_Guarantee)', 'Instaprotek(Device_Guarantee_30days)']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14602,7 +15245,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'InstaProtek (Canada)' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14622,7 +15275,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14642,7 +15305,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (0 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14662,7 +15335,19 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present; download not captured headless: Locator.click: Timeout 30000ms exceeded.
+Call log:
+  - waiti</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14682,7 +15367,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record/modal (1 row(s) matched 'RegressionTest0817'): Edit Administrator | close | Upload | file_upload | Company Name * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14702,7 +15397,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14723,7 +15428,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT'.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14743,7 +15458,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14764,7 +15489,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14797,7 +15532,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Administrator modal: New Administrator | close | Upload | file_upload | Company Name * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14817,7 +15562,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image/upload section exposes a file input (1 present); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14837,7 +15592,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14858,7 +15623,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company name accepts input — field 'Company Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14879,7 +15654,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15796,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Underwriters grid displays (4 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15031,7 +15826,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Underwriters' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15857,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Company Name']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15888,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Company Name'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15094,7 +15919,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dependent dropdown for 'Company Name': ['InstaProtek (Canada)', 'InstaProtek (Japan)', 'InstaProtek (Warranty)', 'InstaProtek Canada', 'Instaprotek Enterprise', 'InstaProtek(CameraProtection)', 'Instaprotek(Device_Guarantee)', 'Instaprotek(Device_Guarantee_30days)']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15116,7 +15951,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'InstaProtek (Canada)' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15136,7 +15981,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15156,7 +16011,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (0 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15176,7 +16041,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Underwriters_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15196,7 +16071,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record (1 row(s) matched 'RegressionTest0817'): Edit Underwriter | close | Upload | file_upload | Company Name * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15216,7 +16101,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15237,7 +16132,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT'.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15257,7 +16162,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15278,7 +16193,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15311,7 +16236,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Underwriter modal: New Underwriter | close | Upload | file_upload | Company Name * | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15331,7 +16266,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image/upload section exposes a file input (1 present); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15351,7 +16296,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15372,7 +16327,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company name accepts input — field 'Company Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15393,7 +16358,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16865,12 +17840,12 @@
           <t>Coverage cost types grid displays (5 rows; columns rendered).</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -16895,12 +17870,12 @@
           <t>'Filter Coverage Cost Types' opens the filter panel with a 'Select a filter' field.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -16926,12 +17901,12 @@
           <t>Filter-field dropdown lists the grid columns: ['Coverage Cost Type', 'Created']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -16957,12 +17932,12 @@
           <t>Selected 'Coverage Cost Type'; it reflects on the field and 'Select a value' appears.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -16988,12 +17963,12 @@
           <t>'Select a value' opens a dependent dropdown for 'Coverage Cost Type': ['Deductible', 'Repair', 'Repair Or Replacement', 'Replacement', 'Shipping &amp; Handling']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17020,12 +17995,12 @@
           <t>Value 'Deductible' selected and reflects on the field; Add Filter becomes available.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17050,12 +18025,12 @@
           <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17080,12 +18055,12 @@
           <t>Search field accepts input and filters the grid (0 rows matched 'a').</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17110,12 +18085,12 @@
           <t>Export downloads 'Coverage_cost_types_08-17-2026.csv'.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17140,12 +18115,12 @@
           <t>Clicking our test record on the grid opens its record/modal (1 row(s) matched 'RegressionTest0817'): Edit Coverage Cost Type Details | close | Coverage Cost Type * | close | Cancel | check | Save &amp; Close</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17170,12 +18145,12 @@
           <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17201,12 +18176,12 @@
           <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT'.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17231,12 +18206,12 @@
           <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17262,12 +18237,12 @@
           <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17305,12 +18280,12 @@
           <t>New opens the New Coverage Cost Type modal: New Coverage Cost Type | close | Coverage Cost Type * | close | Cancel | check | Save &amp; Close</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17336,12 +18311,12 @@
           <t>Coverage cost type name accepts input — field 'Coverage Cost Type *' now reads 'RegressionTest0817'.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -17367,12 +18342,12 @@
           <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -18158,7 +19133,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Review questions grid displays (15 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18178,7 +19163,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Review Questions' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18199,7 +19194,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Title', 'Review Question', 'Option']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18220,7 +19225,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Title'; it reflects on the field and the 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18241,7 +19256,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen column 'Title': ['Clarity and Touch', 'Convenience', 'Design', 'Durability', 'Ease of Installation', 'Ease of Use', 'Installation', 'Length']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18263,7 +19288,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Clarity and Touch' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18283,7 +19318,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18303,7 +19348,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18323,7 +19378,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Review_Question_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18343,7 +19408,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record (1 row(s) matched 'RegressionTest0817'): Edit Review Question Details | close | Title * | Question * | Option * | remove_circle | Option * | remove_circle | Option * | remove</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18363,7 +19438,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18384,7 +19469,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT'.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18404,7 +19499,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18425,7 +19530,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18458,7 +19573,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Review Question modal: New Review Question | close | Title * | Question * | New Option * | Done | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18478,7 +19603,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title accepts input — field 'Title *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18498,7 +19633,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Question accepts input — field 'Question *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18518,7 +19663,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Option accepts input — field 'New Option *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18539,7 +19694,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Selected 'Repair Network Name'; it reflects on the field and 'Select a value' appears.</t>
+          <t>Selected filter column 'Repair Network Name'; it reflects on the field and the 'Select a value' field appears.</t>
         </is>
       </c>
       <c r="F5" s="40" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>'Select a value' opens a dependent dropdown for 'Repair Network Name': []</t>
+          <t>'Select a value' returns no options. The only filter column offered is 'Repair Network Name' and selecting it yields an empty value dropdown even though the grid holds 1 record(s): ['TRG edit delete']. No JavaScript error is raised and the page stays usable. Expected: the value list is populated from the selected column.</t>
         </is>
       </c>
       <c r="F6" s="40" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="G6" s="40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>DEF-SET-02</t>
         </is>
       </c>
     </row>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Value 'None' selected and reflects on the field; Add Filter becomes available.</t>
+          <t>No value could be selected because the dependent value dropdown returns no options (see Grid|5).</t>
         </is>
       </c>
       <c r="F7" s="40" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G7" s="40" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Clicking our test record on the grid opens its record/modal (1 row(s) matched 'RegressionTest0817'): Edit Repair Network Details | close | Repair Network Name * | close | Cancel | check | Save &amp; Continue</t>
+          <t>Clicking our test record on the grid opens its record (1 row(s) matched 'RegressionTest0817'): Edit Repair Network Details | close | Repair Network Name * | close | Cancel | check | Save &amp; Continue</t>
         </is>
       </c>
       <c r="F11" s="40" t="inlineStr">
@@ -16500,7 +16500,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Support grid displays (10 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16530,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Supports' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16541,7 +16561,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Company Name', 'Email', 'Phone', 'Business Hours', 'Website']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16562,7 +16592,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Company Name'; it reflects on the field and the 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16583,7 +16623,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen column 'Company Name': ['InstaProtek (Canada)', 'InstaProtek (Japan)', 'InstaProtek (Warranty)', 'InstaProtek Canada', 'Instaprotek Enterprise', 'InstaProtek(CameraProtection)', 'Instaprotek(Device_Guarantee)', 'Instaprotek(Device_Guarantee_30days)']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16605,7 +16655,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'InstaProtek (Canada)' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16685,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16645,7 +16715,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16745,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Supports_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16775,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record (1 row(s) matched 'RegressionTest0817'): Edit Support | close | Company Name * | Email Address * | Country Code * | CA (+1) | Phone Number | Website * | Business Hours * | La</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16705,7 +16805,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16726,7 +16836,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT regressiontest_0817@qamail.test +1 (415) 555-0188 9:00 AM - 5:00 PM https://example.test edit delete'.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16866,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete "RegressionTest0817-EDIT"? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16767,7 +16897,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16800,7 +16940,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the Support modal: New Support | close | Company Name * | Email Address * | Country Code * | Phone Number | Website * | Business Hours * | Language * | Addre</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16970,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company name accepts input — field 'Company Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16840,7 +17000,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Email address accepts input — field 'Email Address *' now reads 'regressiontest_0817@qamail.test'.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16860,7 +17030,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Click country code field — 'Country Code *' opened; options: ['CA (+1)', 'JP (+81)', 'MX (+52)', 'US (+1)']</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16880,7 +17060,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'CA (+1)' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16900,7 +17090,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone Number accepts input — typing 4155550188 is accepted and the field reflects it in its masked display format "(415) 555-0188".</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16920,7 +17120,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Website accepts input — field 'Website *' now reads 'https://example.test'.</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16940,7 +17150,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Business hours accepts input — field 'Business Hours *' now reads '9:00 AM - 5:00 PM'.</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16960,7 +17180,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Click language field — 'Language *' opened; options: ['English', 'French', 'Japanese']</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16980,7 +17210,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'English' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17240,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Typing an address surfaces suggested result(s) in the autocomplete.</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -17020,7 +17270,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a suggestion reveals the address breakdown sub-form: ['street', 'city', 'zip_code', 'country', 'state']</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -17040,7 +17300,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Notes editor accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17331,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18480,7 +18760,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Shares grid displays (8 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18500,7 +18790,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Shares' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18821,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Store Name', 'Bypass Product Review', 'Show Done Button', 'Done Button Title']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18852,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Store Name'; it reflects on the field and the 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18563,7 +18883,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen column 'Store Name': ['Amazon.com', 'Best Buy', 'Liquipel', 'Simple', 'TestB', 'TESTL', 'TESTW', 'Walmart']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18585,7 +18915,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Amazon.com' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18605,7 +18945,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18625,7 +18975,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18645,7 +19005,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Share_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18665,7 +19035,17 @@
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking our test record on the grid opens its record (1 row(s) matched 'RegressionTest0817'): Edit Share Details | close | Upload Icon | file_upload | Upload Logo | file_upload | Store Name * | Mobile Script | check_box | Bypas</t>
+        </is>
+      </c>
+      <c r="F11" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18685,7 +19065,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The record's name field accepts an edited value 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18706,7 +19096,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the change shows on the grid — row now reads 'RegressionTest0817-EDIT Yes Yes RegressionTest0817 edit delete'.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18726,7 +19126,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal offering Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete RegressionTest0817-EDIT? | close | No | check | Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18747,7 +19157,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No dismisses the dialog and keeps the record (still listed=True); Yes deletes it (removed from grid=True).</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18780,7 +19200,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Share modal: New Share | close | Upload Icon | file_upload | Upload Logo | file_upload | Store Name * | Mobile Script | check_box_outline_blank | Bypas</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18800,7 +19230,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image/upload section exposes a file input (2 present); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18820,7 +19260,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18840,7 +19290,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image/upload section exposes a file input (2 present); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18860,7 +19320,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18880,7 +19350,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store name accepts input — field 'Store Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18900,7 +19380,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Mobile script accepts input — field 'Mobile Script' now reads 'Regression test script'.</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18920,7 +19410,18 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Check bypass product review — checkbox 'check_box
+Bypass Product Review?' toggled False -&gt; True.</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18940,7 +19441,18 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Check is show done button — checkbox 'check_box
+Is Show Done Button?' toggled False -&gt; True.</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18960,7 +19472,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Done button title accepts input — field 'Done Button Title' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -18980,7 +19502,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Review done url accepts input — field 'Review Done URL' now reads 'https://example.test/done'.</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -19001,7 +19533,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave &amp; Close') closes the modal and the new record appears in the grid (listed=True).</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -2817,7 +2817,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device categories grid displays (8 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2847,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Device Categories' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2878,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Device Category Name']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2909,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Device Category Name'; it reflects on the field and the 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2940,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen column 'Device Category Name': ['Chromebook', 'Headphones / Earbuds', 'Laptop', 'Router', 'SmartPhone', 'SmartWatch', 'ta', 'Tablet']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2972,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Chromebook' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2942,7 +3002,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2962,7 +3032,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (0 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2982,7 +3062,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Categories_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3105,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Device Categories modal: New Device Category | close | Upload | file_upload | Device Category Name * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3135,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (1); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3165,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the profile image section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3196,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name accepts input — field 'Device Category Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3227,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the modal and routes to the new record (/category/cbe52212-b439-4f94-8371-19e1cfeb22b4).</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3270,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Devices' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3301,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the sub-grid columns: ['Brand Name', 'Device Name']</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3332,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Brand Name'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3363,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on 'Brand Name' — options ['Acer', 'Asus', 'Dell', 'Hewlett-Packard', 'Lenovo', 'Samsung Galaxy'] (verified on category 'Chromebook', which has 22 device row(s); a newly created category has none, which is why this needs populated data).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3395,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Acer' reflects on the field and applies to the device sub-grid.</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3425,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies and creates a filtered tab in the sub-grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3455,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Sub-grid search accepts input and filters the grid.</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3485,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present on the sub-grid; download not captured headless.</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3516,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t xml:space="preserve">Add opens the Add Devices modal on Step 1: Add Devices | close | 1 | 2 | Step 1 | Select Brand | 	 | Brand Name | arrow_upward |  |  | check_box_outline_blank | 	 | Brand Name | arrow_upward |  |  | 	 | 3Plus | </t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3546,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Brand search inside the modal filters the brand list (1 row(s) matched 'Apple').</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3577,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a brand marks it and enables Next (clicked; Next enabled=True).</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3607,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next routes to Step 2 Select Devices ('chevron_leftPrevious'): Add Devices | close | 1 | 2 | Step 2 | Select Devices | No Records Found! | check_box_outline_blank | 	 | Device Name | arrow_upward |  |  | check_box_outli</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3637,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The Step 2 "Search Devices..." field does not filter the device list. Controlled test on category Chromebook: baseline 22 rows; searching "100e" -&gt; still 22 rows (unchanged, first rows still 100e 4th Gen / 14e Chromebook Gen 3 / 300e 4th Gen); searching "14e" -&gt; still 22; searching a nonsense term "zzzzz" -&gt; still 22 rows after 10s. The field accepts typing but no filtering is applied. Expected: the user should be able to search devices.</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-03</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3668,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a device ticks its checkbox (checked) and enables Save &amp; Close (enabled=True).</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3699,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed by choice: committing Save &amp; Close would permanently add devices to the live category 'Chromebook' on an environment carrying production data. A self-created category cannot be used because its Step 2 device list comes back empty (0 rows), so the commit could only be exercised against real configuration. The modal was verified up to the enabled Save &amp; Close control (enabled=True) and then cancelled.</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3742,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline filter control opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3782,17 @@
       </c>
       <c r="E35" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists timeline columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3813,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3844,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Dependent value dropdown for 'Action': ['Create Category', 'Update Category']</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3876,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Create Category' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3906,17 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the timeline (clicked).</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3936,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline search accepts input and filters the activity list.</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3966,17 @@
       </c>
       <c r="E41" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline records the actions performed on this record — entries: ['Create']. Feed: All Activity | Custom Filter | Custom Filter | Custom Filter | Custom Filter | Custom Filter | arrow_drop_down | Filter Activity | Action is Create Ca</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3639,7 +4009,17 @@
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3659,7 +4039,17 @@
       </c>
       <c r="E44" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3679,7 +4069,17 @@
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3700,7 +4100,17 @@
       </c>
       <c r="E46" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the list (found=True).</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3721,7 +4131,17 @@
       </c>
       <c r="E47" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3742,7 +4162,17 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Change reflects in the title field (True).</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3763,7 +4193,17 @@
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -4389,7 +4389,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product categories grid displays (8 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4419,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Product Categories' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4450,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Product Category Name']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4481,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Product Category Name'; it reflects on the field and the 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4512,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen column 'Product Category Name': ['Cables', 'Camera Lens', 'Case', 'Chargers', 'Power Banks', 'Screen Protectors', 'Smart Tag', 'Tempered Glass']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4544,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Cables' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4574,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4604,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4634,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Categories_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4677,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Product Category modal: New Product Category | close | Upload | file_upload | Product Category Name * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4707,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (1); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4737,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the profile image section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4768,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name accepts input — field 'Product Category Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4799,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the modal and routes to the new record (/product-category/9b983659-4cb8-451d-a64f-c832d28fc854).</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4846,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record details display — uploaded profile image present=True, name shown=True; header: Product Category Details | Navigate | Browse | Product Categories | RegressionTest0817 | Product Category: RegressionTes</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4876,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Products' is the default open tab (tab order: ['Products', 'Timeline', 'Notes']).</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4906,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline tab routes to the timeline panel (True).</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4936,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Notes tab routes to the notes panel (True).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4979,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Products' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4820,7 +5010,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the sub-grid columns: ['Product Barcode', 'Product Name']</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4841,7 +5041,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Product Barcode'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4862,7 +5072,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on 'Product Barcode': ['323666', '810135810081', '810135810098', '810135810548', '810135810944', '810135810982', '810135812023', '810135813181']</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4884,7 +5104,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value '323666' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4904,7 +5134,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies and creates a filtered tab in the sub-grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4924,7 +5164,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Sub-grid search accepts input and filters the grid.</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4944,7 +5194,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Sub-grid exports 'Devices_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4964,7 +5224,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The Products tab of a Product Category record exposes no Add control at all — the only toolbar actions are 'Export as CSV' and 'Filter Products'. Verified on the newly created test category and on three real categories (Cables 27 products, Camera Lens 20, Case 24): no add/add_circle/New button is rendered in any of them. The test case expects an add button that opens an Add Products modal.</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-04</t>
         </is>
       </c>
     </row>
@@ -4984,7 +5254,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Cannot reach searching for a product inside the Add Products modal: the Add Products modal cannot be opened because no Add control exists on the Products tab (see Products|9 / DEF-SET-04).</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5285,17 @@
       </c>
       <c r="E33" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Cannot reach selecting a product: the Add Products modal cannot be opened because no Add control exists on the Products tab (see Products|9 / DEF-SET-04).</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5316,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Cannot reach saving the selected products: the Add Products modal cannot be opened because no Add control exists on the Products tab (see Products|9 / DEF-SET-04).</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5359,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline filter control opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5399,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists timeline columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5430,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5461,17 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The Action value dropdown returns no options because no timeline entries exist for Product Category records at all (see Timeline|8 / DEF-SET-05). Verified with the All Activity filter set selected on both our own test record and the real Cables category.</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-05</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5493,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No value can be selected because the dependent value dropdown is empty — Product Category timelines contain no entries (see Timeline|8 / DEF-SET-05).</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5523,17 @@
       </c>
       <c r="E41" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the timeline (clicked).</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5553,17 @@
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline search accepts input and filters the activity list.</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5583,17 @@
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product Category records do not write any timeline entries. Creating the test product category produced an empty Timeline (No Results Found!), and a long-standing real category (Cables) is also empty with the All Activity filter set explicitly selected. By contrast the equivalent Device Category timeline does log activity (Create Category / Update Category, plus historic entries from May 2024), so timeline logging works elsewhere in the product and is specifically absent for Product Category.</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-05</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5626,17 @@
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5656,17 @@
       </c>
       <c r="E46" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5686,17 @@
       </c>
       <c r="E47" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5717,17 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the list (found=True).</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5748,17 @@
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5779,17 @@
       </c>
       <c r="E50" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Change reflects in the title field (True).</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5810,17 @@
       </c>
       <c r="E51" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -6024,7 +6024,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Brands grid displays (50 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6054,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Brands' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6085,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Brand Name']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6116,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Brand Name'; it reflects on the field and the 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6147,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen column 'Brand Name': ['3Plus', 'Accent', 'Accutime', 'Acer', 'Advance', 'Agptek', 'Alcatel', 'AliExpress']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6179,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value '3Plus' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6209,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6239,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (1 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6269,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Brands_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6312,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Brand modal: New Brand | close | Upload | file_upload | Brand Name * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6342,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (1); clicking it opens the OS file explorer (native dialog, not scriptable headless).</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6372,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the profile image section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6403,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name accepts input — field 'Brand Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6434,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the modal and routes to the new record (/brand/a3581868-bb6d-41fc-9aa2-7762ac2ffb26).</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6481,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record details display — uploaded profile image present=True, name shown=True; header: Brand Details | Navigate | Browse | Brands | RegressionTest0817 | Brand: RegressionTest0817 | keyboard_arrow_left | 1 of 176</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6511,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Devices' is the default open tab (tab order: ['Devices', 'Timeline', 'Notes']).</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6541,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline tab routes to the timeline panel (True).</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6571,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Notes tab routes to the notes panel (True).</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6613,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Device Categories' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6644,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the sub-grid columns: ['Device Name', 'Categories', 'Internet Connection Type', 'Bypass Screen Test', 'Protection Coverage', 'IMEI', 'MEID', 'Serial Number']</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6675,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Device Name'; it reflects on the field and 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6706,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on 'Device Name': ['RegressionTest0817']</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6738,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'RegressionTest0817' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6768,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies and creates a filtered tab in the sub-grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6798,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Sub-grid search accepts input and filters the grid.</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6828,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Sub-grid exports 'Devices_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6858,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The brand's device grid renders (0 device row(s) for the newly created brand).</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6888,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Device modal: New Device | close | Upload | file_upload | Device Name * | Identifier | Categories * | Internet Connection Type |  | Device ID Type |  | check_box | IMEI</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6918,17 @@
       </c>
       <c r="E33" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (1); clicking it opens the OS file explorer.</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6948,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the profile image section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6978,17 @@
       </c>
       <c r="E35" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device name accepts input — field 'Device Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6698,7 +7008,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'identifier' field opens a dropdown — 'Identifier' opened; options: ['Watch5,12', 'iPad2,2', 'Watch6,4', '15,7', 'CPH2599', 'iPad12,1', 'iPad12,2', 'Ipad13, 8']</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6718,7 +7038,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Watch5,12' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6738,7 +7068,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'categor' field opens a dropdown — 'Categories *' opened; options: ['Chromebook', 'Headphones / Earbuds', 'Laptop', 'Router', 'SmartPhone', 'SmartWatch', 'ta', 'Tablet']</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6758,7 +7098,17 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Chromebook' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6778,7 +7128,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'internet connection' field opens a dropdown — 'Internet Connection Type' opened; options: ['Cellular', 'Ethernet', 'None', 'Satellite', 'WiFi']</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6798,7 +7158,17 @@
       </c>
       <c r="E41" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Cellular' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6818,7 +7188,17 @@
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>IMEI is the default selected Device ID Type — checked on load: ['IMEI']; the Device ID Type group offers ['IMEI', 'MEID', 'Serial Number'] (rendered as checkboxes, not radio buttons).</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6838,7 +7218,17 @@
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting another Device ID type checks it — {'label': 'MEID', 'checked': True}.</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6858,7 +7248,17 @@
       </c>
       <c r="E44" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a workflow option checks it — {'label': 'Bypass screen test', 'checked': True}.</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6879,7 +7279,17 @@
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the device record is created.</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6911,7 +7321,17 @@
       </c>
       <c r="E47" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline filter control opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6941,7 +7361,17 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists timeline columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6962,7 +7392,17 @@
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6983,7 +7423,17 @@
       </c>
       <c r="E50" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Dependent value dropdown for 'Action': ['Create Brand', 'Update Brand']</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7455,17 @@
       </c>
       <c r="E51" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Create Brand' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7485,17 @@
       </c>
       <c r="E52" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the timeline (clicked).</t>
+        </is>
+      </c>
+      <c r="F52" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7515,17 @@
       </c>
       <c r="E53" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline search accepts input and filters the activity list.</t>
+        </is>
+      </c>
+      <c r="F53" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7545,17 @@
       </c>
       <c r="E54" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline records the actions performed on this record — entries: ['Create']. Feed: keyboard_arrow_left | keyboard_arrow_right | All Activity | Custom Filter | Custom Filter | Custom Filter | Custom Filter | Custom Filter | Custom Fil</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7588,17 @@
       </c>
       <c r="E56" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F56" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7618,17 @@
       </c>
       <c r="E57" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F57" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7648,17 @@
       </c>
       <c r="E58" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F58" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7679,17 @@
       </c>
       <c r="E59" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the list (found=True).</t>
+        </is>
+      </c>
+      <c r="F59" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7710,17 @@
       </c>
       <c r="E60" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
+        </is>
+      </c>
+      <c r="F60" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7741,17 @@
       </c>
       <c r="E61" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Change reflects in the title field (True).</t>
+        </is>
+      </c>
+      <c r="F61" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G61" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7772,17 @@
       </c>
       <c r="E62" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F62" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -7986,7 +7986,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Created registration survey questions display on the grid — 3 question row(s) listed, e.g. ['menu Do you currently have insurance on your device? edit delete', 'menu Have you purchased your device in the past 60 days? edit delete'].</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8016,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the question record in a modal with its details populated — question field reads 'RegressionTest0817 survey question?'. Row controls: {'btns': ['edit', 'edit', 'delete', 'delete'], 'cls': 'sortable-list-content'}</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8047,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The question can be updated — field now reads 'RegressionTest0817 survey question edited?' (True).</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8078,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the change is saved — the edited question is listed on reload (True).</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8108,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirmation modal with Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete "RegressionTest0817 survey question edited?"? | close | No | check | Y</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8139,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking No closes the modal and cancels the delete — the question is still listed (True).</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8170,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking Yes closes the modal and deletes the selected question — removed from the grid (True).</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -7989,12 +7989,12 @@
           <t>Created registration survey questions display on the grid — 3 question row(s) listed, e.g. ['menu Do you currently have insurance on your device? edit delete', 'menu Have you purchased your device in the past 60 days? edit delete'].</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8019,12 +8019,12 @@
           <t>Edit (clicked) opens the question record in a modal with its details populated — question field reads 'RegressionTest0817 survey question?'. Row controls: {'btns': ['edit', 'edit', 'delete', 'delete'], 'cls': 'sortable-list-content'}</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8050,12 +8050,12 @@
           <t>The question can be updated — field now reads 'RegressionTest0817 survey question edited?' (True).</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8081,12 +8081,12 @@
           <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the change is saved — the edited question is listed on reload (True).</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8111,12 +8111,12 @@
           <t>Delete shows a confirmation modal with Yes/No (clicked): Delete Confirmation | close | Are you sure you want to delete "RegressionTest0817 survey question edited?"? | close | No | check | Y</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8142,12 +8142,12 @@
           <t>Clicking No closes the modal and cancels the delete — the question is still listed (True).</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8173,12 +8173,12 @@
           <t>Clicking Yes closes the modal and deletes the selected question — removed from the grid (True).</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -8366,7 +8366,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans grid displays (50 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8396,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Plans' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8427,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Plan Name', 'Plan Code', 'Region', 'Coverage Amount', 'Coverage Period', 'Terms', 'SKU', 'Administrator', 'Underwriter', 'Support', 'Coverage Type', 'Coverage Cost Type', 'Coverage Type Amount', 'Channel']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8458,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Plan Name'; it reflects on the field and the 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8489,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen column 'Plan Name': ['2 - Years Warranty Replacement', 'Camera Protection 100', 'Demo Plan 100', 'Device Protection 100', 'Enterprise Case + Screen Product Guarantee - 12 Months', 'Enterprise Case + Screen Product Guarantee - 36 Months', 'Enterprise Case + Screen Protector Product Guarantee - 24 Months', 'Enterprise Case Guarantee and Extended Service Warranty - 48 Months']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8521,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value '2 - Years Warranty Replacement' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8551,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8581,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (50 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8611,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'ProductPlan_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8655,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Plan modal on Step 1: New Plan | close | 1 | 2 | 3 | Step 1 | Plan Details | Upload | file_upload | Plan Name * | Region * | Coverage Amount * | SKU | Administrator * | Underwriter</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8685,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (2); clicking it opens the OS file explorer.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8715,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the profile image section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8745,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan name accepts input — field 'Plan Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8775,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No "Plan Type" field exists on the New Plan form. Step 1 (Plan Details) renders exactly: Plan Name*, Region*, Coverage Amount*, SKU, Administrator*, Underwriter*, Coverage Type*, Coverage Cost Type*, Coverage Period (Year/s)*, Coverage Type Amount*, Channel* — plus the image upload. The words "Single"/"Multiple" do not appear anywhere in the form. The test cases expect a Plan Type field defaulting to "Single" with a dropdown of other plan types.</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-06</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8805,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>There is no Plan Type field to click — see New Plan|5 / DEF-SET-06. (An earlier automated pass matched the "Coverage Type Amount" dropdown by label similarity; on re-inspection of the rendered form no Plan Type control exists.)</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-06</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8835,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No plan type can be selected because the field does not exist — see New Plan|5 / DEF-SET-06.</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-06</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8865,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Region field opens a dropdown — 'Region *' opened; options: ['Canada', 'Puerto Rico', 'United Kingdom', 'United States']</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8895,17 @@
       </c>
       <c r="E20" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected region 'Canada' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8925,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>SKU accepts input — field 'SKU' now reads 'REGTEST-SKU-0817'.</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8955,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Administrator field opens a dropdown — 'Administrator *' opened; options: ['After Inc.', 'InstaProtek', 'Liquipel', 'The Plateau Group Inc.']</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8785,7 +8985,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected administrator 'After Inc.' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8805,7 +9015,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Underwriter field opens a dropdown — 'Underwriter *' opened; options: ['Ensure Protect', 'InstaProtek', 'Mobilio', 'STARR Companies']</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8825,7 +9045,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected underwriter 'Ensure Protect' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8845,7 +9075,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage type field opens a dropdown — 'Coverage Type Amount *' opened; options: ['Camera Repair Guarantee', 'Case &amp; Screen Protector Guarantee', 'Case Guarantee', 'Device Guarantee Excluding Screen Repair', 'Product Replacement', 'Repair Guarantee', 'Repair Or Replacement', 'Screen Coverage']</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8865,7 +9105,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected coverage type 'Camera Repair Guarantee' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8885,7 +9135,17 @@
       </c>
       <c r="E28" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage cost type field opens a dropdown — 'Coverage Cost Type *' opened; options: ['Deductible', 'Repair', 'Repair Or Replacement', 'Replacement', 'Shipping &amp; Handling']</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8905,7 +9165,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage period accepts input — field 'Coverage Period (Year/s) *' now reads '12'.</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8925,7 +9195,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Channel field opens a dropdown — 'Channel *' opened; options: ['Call Center', 'Online', 'Retail']</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8945,7 +9225,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected channel 'Call Center' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8965,7 +9255,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next routes to Step 2 Support &amp; Term Details ('chevron_leftPrevious'): New Plan | close | 1 | 2 | 3 | Step 2 | Support &amp; Term Details | Support * | Terms * | Upload PDF File | file_upload | close | Cancel | chevron_left | Previous | chevron_</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8985,7 +9285,17 @@
       </c>
       <c r="E33" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Support field opens a dropdown — 'Support *' opened; options: ['InstaProtek (Canada)', 'InstaProtek (Japan)', 'InstaProtek (Warranty)', 'InstaProtek Canada', 'Instaprotek Enterprise', 'InstaProtek_Guarantee(30 days)', 'InstaProtek(CameraProtection)', 'Instaprotek(Device_Guarantee_30days)']</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9315,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected support 'InstaProtek (Canada)' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9025,7 +9345,17 @@
       </c>
       <c r="E35" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Upload PDF control present (2 file input(s)); clicking it opens the OS file explorer.</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9045,7 +9375,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected PDF reflects in the terms section (filename shown=True).</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9405,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next routes to Step 3 Summary ('checkSave &amp; Continue'): New Plan | close | 1 | 2 | 3 | Step 3 | Summary | Plan Details | Plan Name: | RegressionTest0817 | Region: | Canada | Coverage Amount: | CAD 0.00 | SKU: | REGTEST-SKU-081</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9085,7 +9435,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Summary shows the plan details entered in Step 1 (plan name 'RegressionTest0817' present=True).</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9465,17 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Summary shows the Step 2 support &amp; term details — ['Support', 'Terms', 'Term', 'terms_test'].</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9497,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Continue') closes the modal and routes to the plan record (/product-plans/cda97358-a37b-4fb8-8489-109c37bb12ee).</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9547,17 @@
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan record details display — image present=True, plan name shown=True; header: Plan Details | Navigate | Browse | Plans | RegressionTest0817 | Plan: RegressionTest0817 | keyboard_arrow_left | 37 of 55 | ke</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9187,7 +9577,17 @@
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The plan name field (textarea#name) accepts an updated value — 'RegressionTest0817' -&gt; 'RegressionTest0817-EDIT' (True).</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9607,17 @@
       </c>
       <c r="E44" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave and Close') persists the change — the plans grid row now reads 'RegressionTest0817-EDIT Canada CAD 0.00 12 terms_test.pdf REGTEST-SKU-0817 After'.</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9637,17 @@
       </c>
       <c r="E45" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Details' is the default open tab (tab order: ['Details', 'Timeline', 'Notes']).</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9667,17 @@
       </c>
       <c r="E46" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline tab routes to the timeline panel.</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9697,17 @@
       </c>
       <c r="E47" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Notes tab routes to the notes panel.</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9740,17 @@
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan details entered during creation are displayed — ['Plan Name', 'Region', 'SKU', 'Administrator', 'Underwriter', 'Coverage'].</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9770,17 @@
       </c>
       <c r="E50" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>A Details field accepts an updated value 'RegressionTest0817-DET' (True).</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9800,17 @@
       </c>
       <c r="E51" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave and Close') persists the details change — grid row reads 'RegressionTest0817-DET Canada CAD 0.00 12 terms_test.pdf REGTEST-SKU-0817 After '.</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9843,17 @@
       </c>
       <c r="E53" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline filter control opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F53" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9883,17 @@
       </c>
       <c r="E54" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists timeline columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9914,17 @@
       </c>
       <c r="E55" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F55" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G55" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9445,7 +9945,17 @@
       </c>
       <c r="E56" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Dependent value dropdown for 'Action': ['Create Plan', 'Update Plan']</t>
+        </is>
+      </c>
+      <c r="F56" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9977,17 @@
       </c>
       <c r="E57" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Create Plan' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F57" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9487,7 +10007,17 @@
       </c>
       <c r="E58" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the timeline (clicked).</t>
+        </is>
+      </c>
+      <c r="F58" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9507,7 +10037,17 @@
       </c>
       <c r="E59" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline search accepts input and filters the activity list.</t>
+        </is>
+      </c>
+      <c r="F59" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9527,7 +10067,17 @@
       </c>
       <c r="E60" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline records the actions performed on this record — entries: ['Create']. Feed: keyboard_arrow_left | keyboard_arrow_right | All Activity | Custom Filter | Custom Filter | Custom Filter | Custom Filter | Custom Filter | Custom Fil</t>
+        </is>
+      </c>
+      <c r="F60" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9560,7 +10110,17 @@
       </c>
       <c r="E62" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F62" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9580,7 +10140,17 @@
       </c>
       <c r="E63" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F63" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G63" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9600,7 +10170,17 @@
       </c>
       <c r="E64" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F64" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G64" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9621,7 +10201,17 @@
       </c>
       <c r="E65" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the list (found=True).</t>
+        </is>
+      </c>
+      <c r="F65" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G65" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9642,7 +10232,17 @@
       </c>
       <c r="E66" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
+        </is>
+      </c>
+      <c r="F66" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G66" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9663,7 +10263,17 @@
       </c>
       <c r="E67" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Change reflects in the title field (True).</t>
+        </is>
+      </c>
+      <c r="F67" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G67" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -9684,7 +10294,17 @@
       </c>
       <c r="E68" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F68" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G68" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -11154,7 +11154,17 @@
       </c>
       <c r="E2" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Companies grid displays (25 rows; columns rendered).</t>
+        </is>
+      </c>
+      <c r="F2" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G2" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11184,17 @@
       </c>
       <c r="E3" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Companies' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F3" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11215,17 @@
       </c>
       <c r="E4" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the grid columns: ['Company Name', 'Company Phone', 'Products', 'Enable Enterprise Program']</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11246,17 @@
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Company Name'; it reflects on the field and the 'Select a value' field appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11277,17 @@
       </c>
       <c r="E6" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on the chosen column 'Company Name': ['C2 Wireless', 'ChromebookParts.com', 'Connected Solutions Group, LLC', 'Device Solutions LLC', 'Elecom', 'Eternize', 'EyeJust', 'Fides Communication LLC']</t>
+        </is>
+      </c>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11309,17 @@
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'C2 Wireless' selected and reflects on the field; Add Filter becomes available.</t>
+        </is>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11339,17 @@
       </c>
       <c r="E8" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies the filter and creates a filtered tab in the grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11369,17 @@
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (0 rows matched 'a').</t>
+        </is>
+      </c>
+      <c r="F9" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11399,17 @@
       </c>
       <c r="E10" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export downloads 'Company_08-17-2026.csv'.</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11442,17 @@
       </c>
       <c r="E12" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the New Company modal: New Company | close | Upload | file_upload | Company Name * | Country Code * | Phone Number * | close | Cancel | check | Save &amp; Continue</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11372,7 +11472,17 @@
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (1); clicking it opens the OS file explorer.</t>
+        </is>
+      </c>
+      <c r="F13" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11392,7 +11502,17 @@
       </c>
       <c r="E14" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects in the profile image section — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11532,17 @@
       </c>
       <c r="E15" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company name accepts input — field 'Company Name *' now reads 'RegressionTest0817'.</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11562,17 @@
       </c>
       <c r="E16" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Country code field opens a dropdown — 'Country Code *' opened; options: ['CA (+1)', 'JP (+81)', 'MX (+52)', 'US (+1)']</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11592,17 @@
       </c>
       <c r="E17" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected country code 'CA (+1)' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11622,17 @@
       </c>
       <c r="E18" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone number accepts input — field 'Phone Number *' now reads '(415) 555-0199'.</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11493,7 +11653,17 @@
       </c>
       <c r="E19" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the modal and routes to the company record (/company/f4957bcc-4b0f-4dc1-9fcd-a7b98f48eb54).</t>
+        </is>
+      </c>
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11530,7 +11700,17 @@
       </c>
       <c r="E21" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company record details display — image present=True, name shown=True; tabs ['Details', 'Users', 'Plans', 'Products', 'Timeline', 'Notes'].</t>
+        </is>
+      </c>
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11730,17 @@
       </c>
       <c r="E22" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Details' is the default open tab (tab order: ['Details', 'Users', 'Plans', 'Products', 'Timeline', 'Notes']).</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11570,7 +11760,17 @@
       </c>
       <c r="E23" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Users' tab routes to its panel.</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11790,17 @@
       </c>
       <c r="E24" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Plans' tab routes to its panel.</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11820,17 @@
       </c>
       <c r="E25" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Products' tab routes to its panel.</t>
+        </is>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11850,17 @@
       </c>
       <c r="E26" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Timeline' tab routes to its panel.</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11650,7 +11880,17 @@
       </c>
       <c r="E27" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Notes' tab routes to its panel.</t>
+        </is>
+      </c>
+      <c r="F27" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11924,17 @@
       </c>
       <c r="E29" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Enterprise Program section displayed (True). Panel: Company Details | Navigate | Browse | Companies | RegressionTest0817 | Company: RegressionTest0817 | keyboard_arrow_left | 19 of 26 | ke</t>
+        </is>
+      </c>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11707,7 +11957,17 @@
       </c>
       <c r="E30" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details section displayed. Panel mentions: ['Company Details', 'Company Name']</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11996,17 @@
       </c>
       <c r="E31" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Enabling the Enterprise Program ({'before': False, 'label': 'Enable Enterprise Program'}) reveals the additional company-details fields — now rendered: ['name', 'enable_enterprise_program', 'company_code', 'repair_network', 'country_lu', 'first_name', 'last_name', 'email', 'phone_code', 'phone'].</t>
+        </is>
+      </c>
+      <c r="F31" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11756,7 +12026,17 @@
       </c>
       <c r="E32" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company code accepts input — #company_code now reads 'REGTEST0817'.</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11776,7 +12056,17 @@
       </c>
       <c r="E33" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Repair network field opens a dropdown; options: ['TRG']</t>
+        </is>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11796,7 +12086,17 @@
       </c>
       <c r="E34" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected repair network 'TRG' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11816,7 +12116,17 @@
       </c>
       <c r="E35" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No 'Device Management System' field exists on the company Details form. The only dropdowns rendered after enabling the Enterprise Program are ['Repair Network', 'Country *', 'CA (+1)'] (ids: repair_network, country_lu, phone_code); the text inputs are Company Name, Company Code, First Name, Last Name, Email, Phone. The test case expects a Device Management System dropdown.</t>
+        </is>
+      </c>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G35" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-07</t>
         </is>
       </c>
     </row>
@@ -11836,7 +12146,17 @@
       </c>
       <c r="E36" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No device management system option can be selected because the field does not exist (see Details|7 / DEF-SET-07).</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G36" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11856,7 +12176,17 @@
       </c>
       <c r="E37" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Country field (#country_lu) opens a dropdown; options: ['Canada', 'Puerto Rico', 'United Kingdom', 'United States']</t>
+        </is>
+      </c>
+      <c r="F37" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11876,7 +12206,17 @@
       </c>
       <c r="E38" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected country 'United States' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11896,7 +12236,17 @@
       </c>
       <c r="E39" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>First name accepts input — #first_name now reads 'RegressionTest'.</t>
+        </is>
+      </c>
+      <c r="F39" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11916,7 +12266,17 @@
       </c>
       <c r="E40" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Last name accepts input — #last_name now reads 'CompanyAug17'.</t>
+        </is>
+      </c>
+      <c r="F40" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11936,7 +12296,17 @@
       </c>
       <c r="E41" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Email address accepts input — #email now reads 'regressiontest_co_0817@qamail.test'.</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11956,7 +12326,17 @@
       </c>
       <c r="E42" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Typing an address surfaces suggested result(s) in the autocomplete.</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11976,7 +12356,17 @@
       </c>
       <c r="E43" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a suggestion reveals the address breakdown sub-form: ['street', 'city', 'zip_code', 'country', 'state']</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11996,7 +12386,17 @@
       </c>
       <c r="E44" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave and Close') stores the company details — reopened the record: Enterprise Program still enabled=True, fields {'code': 'REGTEST0817', 'first': 'RegressionTest', 'email': 'regressiontest_co_0817@qamail.test'}.</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -12430,7 +12430,17 @@
       </c>
       <c r="E46" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users grid displays inside the company record (0 row(s)).</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12450,7 +12460,17 @@
       </c>
       <c r="E47" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Users' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12491,17 @@
       </c>
       <c r="E48" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the columns: ['Email', 'First Name', 'Last Name', 'Role', 'Allow Device Buyback', 'Company', 'User Type', 'Affiliate', 'Status']</t>
+        </is>
+      </c>
+      <c r="F48" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12522,17 @@
       </c>
       <c r="E49" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Email'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F49" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12553,17 @@
       </c>
       <c r="E50" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on 'Email': ['aatef@liquipel.com', 'admin@dnamicro.com', 'admin@instaprotek.com', 'agentqa@dnamicro.com', 'aj.crook@d428.org', 'ajuson@dnamicro.com', 'akarey@bcps.org', 'akennedy@laurelchristian.org']</t>
+        </is>
+      </c>
+      <c r="F50" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G50" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12585,17 @@
       </c>
       <c r="E51" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'aatef@liquipel.com' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G51" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12615,17 @@
       </c>
       <c r="E52" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies and creates a filtered tab (clicked).</t>
+        </is>
+      </c>
+      <c r="F52" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G52" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12575,7 +12645,17 @@
       </c>
       <c r="E53" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid.</t>
+        </is>
+      </c>
+      <c r="F53" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G53" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12595,7 +12675,17 @@
       </c>
       <c r="E54" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present; download not captured headless.</t>
+        </is>
+      </c>
+      <c r="F54" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G54" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12705,17 @@
       </c>
       <c r="E55" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No resend-invite row action is rendered on the users grid. Company 'C2 Wireless' with 1 user(s) exposes only these row actions: ['edit', 'edit', 'lock', 'lock', 'remove_circle', 'remove_circle']. The test case expects a resend-invite action on the grid.</t>
+        </is>
+      </c>
+      <c r="F55" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G55" s="40" t="inlineStr">
+        <is>
+          <t>DEF-SET-08</t>
         </is>
       </c>
     </row>
@@ -12636,7 +12736,17 @@
       </c>
       <c r="E56" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the add-user modal: New User | close | 1 | 2 | Step 1  | Search User | arrow_drop_down | Filter User | 	 | Email | arrow_upward | 	 | First Name | arrow_upward | 	 | Last Name | arro</t>
+        </is>
+      </c>
+      <c r="F56" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G56" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12767,17 @@
       </c>
       <c r="E57" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The add-user modal opens directly on the user-selection step; its controls are ['keyboard_arrow_right', 'vertical_align_top', 'remove_red_eye', 'closeCancel', 'chevron_rightNext'] (no Yes/No prompt is presented on this build).</t>
+        </is>
+      </c>
+      <c r="F57" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G57" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12797,17 @@
       </c>
       <c r="E58" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t xml:space="preserve">Existing users are listed in the modal (34 row(s)): New User | close | 1 | 2 | Step 1  | Search User | arrow_drop_down | Filter User | 	 | Email | arrow_upward | 	 | First </t>
+        </is>
+      </c>
+      <c r="F58" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G58" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12697,7 +12827,17 @@
       </c>
       <c r="E59" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>User search inside the modal returns 34 row(s).</t>
+        </is>
+      </c>
+      <c r="F59" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G59" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12857,17 @@
       </c>
       <c r="E60" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a user marks its row (checked).</t>
+        </is>
+      </c>
+      <c r="F60" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G60" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12737,7 +12887,17 @@
       </c>
       <c r="E61" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next advances the add-user flow ('Loading...').</t>
+        </is>
+      </c>
+      <c r="F61" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G61" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12757,7 +12917,17 @@
       </c>
       <c r="E62" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The selected user's details populate the fields ({'total': 51, 'filled': 8, 'ids': ['dnaTable2-searchField', 'undefined-1', 'undefined-2', 'undefined-3', 'undefined-4', 'undefined-5', 'undefined-6', 'undefined-7', 'undefined-8', 'undefined-9']}).</t>
+        </is>
+      </c>
+      <c r="F62" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G62" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12778,7 +12948,17 @@
       </c>
       <c r="E63" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>An Add/Save control is available to complete adding the user: ['vertical_align_top', 'closeCancel', 'chevron_leftPrevious', 'chevron_rightAdd User']</t>
+        </is>
+      </c>
+      <c r="F63" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G63" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12979,17 @@
       </c>
       <c r="E64" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The step requires the user-details form to be completed — required fields shown: ['Email *', '1', 'User Type *', 'Reseller *', 'Phone Number *', 'Address *location_onOther', 'Street *', 'City *', 'Postal Code *'].</t>
+        </is>
+      </c>
+      <c r="F64" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G64" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12833,7 +13023,17 @@
       </c>
       <c r="E66" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans grid displays inside the company record (0 row(s)).</t>
+        </is>
+      </c>
+      <c r="F66" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G66" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12853,7 +13053,17 @@
       </c>
       <c r="E67" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Plans' opens the filter panel with a 'Select a filter' field.</t>
+        </is>
+      </c>
+      <c r="F67" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G67" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12874,7 +13084,17 @@
       </c>
       <c r="E68" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the columns: ['Plan Name', 'Plan Code', 'Region', 'Coverage Amount', 'Coverage Period', 'Terms', 'SKU', 'Administrator', 'Underwriter', 'Support', 'Coverage Type', 'Coverage Cost Type', 'Coverage Type Amount', 'Channel']</t>
+        </is>
+      </c>
+      <c r="F68" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G68" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12895,7 +13115,17 @@
       </c>
       <c r="E69" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Plan Name'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F69" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G69" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12916,7 +13146,17 @@
       </c>
       <c r="E70" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on 'Plan Name' now the company has a plan: ['2 - Years Warranty Replacement']</t>
+        </is>
+      </c>
+      <c r="F70" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G70" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12938,7 +13178,17 @@
       </c>
       <c r="E71" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value '2 - Years Warranty Replacement' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F71" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G71" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12958,7 +13208,17 @@
       </c>
       <c r="E72" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies and creates a filtered tab (clicked).</t>
+        </is>
+      </c>
+      <c r="F72" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G72" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12978,7 +13238,17 @@
       </c>
       <c r="E73" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid.</t>
+        </is>
+      </c>
+      <c r="F73" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G73" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12998,7 +13268,17 @@
       </c>
       <c r="E74" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present; download not captured headless.</t>
+        </is>
+      </c>
+      <c r="F74" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G74" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13298,17 @@
       </c>
       <c r="E75" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the add-plan modal: Add New Plan | close | 1 | 2 | check_box_outline_blank | 	 | Plan Name | arrow_upward | 	 | Coverage Amount | arrow_upward | 	 | Coverage Period | arrow_upw</t>
+        </is>
+      </c>
+      <c r="F75" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G75" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13328,17 @@
       </c>
       <c r="E76" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No image/upload control exists in the company's Add New Plan modal. The modal is a two-step plan picker (Step 1 lists existing plans to select, Step 2 captures the Plan Code) and contains 0 file inputs. Modal: Add New Plan | close | 1 | 2 | check_box_outline_blank | 	 | Plan Name | arrow_upward | 	 | Coverage Amount | arrow_upward | 	 | Coverage Period | arrow_upw. The test case expects a profile image section.</t>
+        </is>
+      </c>
+      <c r="F76" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G76" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13358,17 @@
       </c>
       <c r="E77" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No image control exists in the add-plan modal (see Plans|11).</t>
+        </is>
+      </c>
+      <c r="F77" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G77" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13078,7 +13388,17 @@
       </c>
       <c r="E78" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The add-plan modal presents its controls: ['keyboard_arrow_left', 'keyboard_arrow_right', 'vertical_align_top', 'closeCancel', 'checkSelect Plan']</t>
+        </is>
+      </c>
+      <c r="F78" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G78" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13098,7 +13418,17 @@
       </c>
       <c r="E79" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans from the main Plans menu are listed in the modal (50 row(s)): Add New Plan | close | 1 | 2 | check_box_outline_blank | 	 | Plan Name | arrow_upward | 	 | Coverage Amount | arrow_upwa</t>
+        </is>
+      </c>
+      <c r="F79" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G79" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13449,17 @@
       </c>
       <c r="E80" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting a plan marks its row (checked).</t>
+        </is>
+      </c>
+      <c r="F80" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G80" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13139,7 +13479,17 @@
       </c>
       <c r="E81" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The select-plan action advances the flow ('chevron_leftPrevious').</t>
+        </is>
+      </c>
+      <c r="F81" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G81" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13510,17 @@
       </c>
       <c r="E82" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan code accepts input — field 'Plan Code *' now reads 'REGTESTPLAN0817'.</t>
+        </is>
+      </c>
+      <c r="F82" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G82" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13542,17 @@
       </c>
       <c r="E83" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save attaches the selected plan to the company — the company's Plans grid now holds 1 row: '2 - Years Warranty Replacement REGTESTPLAN0817 United States USD 0.00 2 Terms and Conditions_Warranty_Replacem' (plan code REGTESTPLAN0817 applied).</t>
+        </is>
+      </c>
+      <c r="F83" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G83" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13203,7 +13573,17 @@
       </c>
       <c r="E84" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>A plan record opens from the company's plan grid (ok); tabs now ['Details', 'Batches', 'Timeline', 'Notes'].</t>
+        </is>
+      </c>
+      <c r="F84" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G84" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13223,7 +13603,17 @@
       </c>
       <c r="E85" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Batches tab is present and routes to its panel (True); tabs ['Details', 'Batches', 'Timeline', 'Notes'].</t>
+        </is>
+      </c>
+      <c r="F85" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G85" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13634,17 @@
       </c>
       <c r="E86" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Batches grid displays (0 batch row(s)).</t>
+        </is>
+      </c>
+      <c r="F86" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G86" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13664,17 @@
       </c>
       <c r="E87" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Batches' opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F87" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G87" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13695,17 @@
       </c>
       <c r="E88" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists batch columns: ['Batch Number', 'Product', 'Product Barcode', 'Expiration Date', 'Number of Pins', 'Pins Used', 'Available Pins', 'Plan Purchase Date', 'Status', 'Use for Registration']</t>
+        </is>
+      </c>
+      <c r="F88" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G88" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13726,17 @@
       </c>
       <c r="E89" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected batch filter column 'Batch Number'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F89" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G89" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13757,17 @@
       </c>
       <c r="E90" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select a value' opens a dropdown dependent on 'Batch Number' with 1 batch row(s) present: ['9580']</t>
+        </is>
+      </c>
+      <c r="F90" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G90" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13349,7 +13789,17 @@
       </c>
       <c r="E91" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value '9580' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F91" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G91" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13369,7 +13819,17 @@
       </c>
       <c r="E92" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the batches grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F92" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G92" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13389,7 +13849,17 @@
       </c>
       <c r="E93" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Batches search accepts input and filters the grid.</t>
+        </is>
+      </c>
+      <c r="F93" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G93" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13879,17 @@
       </c>
       <c r="E94" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present on the batches grid; download not captured headless.</t>
+        </is>
+      </c>
+      <c r="F94" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G94" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13909,17 @@
       </c>
       <c r="E95" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t xml:space="preserve">New opens the New Batch modal: New Batch | close | Product | Product | Number of Pins * | Expiration Date (mm/dd/yyyy) * | PO Number | Invoice Number |  | Workflow |  | check_box | Use </t>
+        </is>
+      </c>
+      <c r="F95" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G95" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13940,17 @@
       </c>
       <c r="E96" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product field opens but returns no options — the plan attached to this company has no products associated with it yet, so there is nothing to choose. (The field itself renders and is clickable.)</t>
+        </is>
+      </c>
+      <c r="F96" s="40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="G96" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13970,17 @@
       </c>
       <c r="E97" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No product option can be selected because the dropdown returns no options (see Plans|31).</t>
+        </is>
+      </c>
+      <c r="F97" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G97" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13490,7 +14000,17 @@
       </c>
       <c r="E98" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Number of pins accepts input — field 'Number of Pins *' now reads '5'.</t>
+        </is>
+      </c>
+      <c r="F98" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G98" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13510,7 +14030,17 @@
       </c>
       <c r="E99" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan Purchase Date field is present in the New Batch modal ({'id': None, 'label': 'Plan Purchase Date (mm/dd/yyyy) *'}); it accepts a typed mm/dd/yyyy date and also offers a picker.</t>
+        </is>
+      </c>
+      <c r="F99" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G99" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13530,7 +14060,17 @@
       </c>
       <c r="E100" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>A date can be set on the Plan Purchase Date field — field now reads '08/17/2026'.</t>
+        </is>
+      </c>
+      <c r="F100" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G100" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13550,7 +14090,17 @@
       </c>
       <c r="E101" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Vertical field opens a dropdown — 'Vertical *' opened; options: ['Education', 'State/Local Government', 'Healthcare', 'Hospitality', 'Utilities', 'Retail', 'Transportation']</t>
+        </is>
+      </c>
+      <c r="F101" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G101" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13570,7 +14120,17 @@
       </c>
       <c r="E102" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected vertical 'Education' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F102" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G102" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -13591,7 +14151,17 @@
       </c>
       <c r="E103" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the New Batch modal and creates the batch.</t>
+        </is>
+      </c>
+      <c r="F103" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G103" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
+++ b/Insta-testing/Regression_QA_Log_NULLNET-2026-08-17.xlsx
@@ -3647,7 +3647,7 @@
       </c>
       <c r="G30" s="40" t="inlineStr">
         <is>
-          <t>DEF-SET-03</t>
+          <t>DEF-SET-03 / INSTA-1406</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G39" s="40" t="inlineStr">
         <is>
-          <t>DEF-SET-05</t>
+          <t>DEF-SET-05 / INSTA-1407</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="G43" s="40" t="inlineStr">
         <is>
-          <t>DEF-SET-05</t>
+          <t>DEF-SET-05 / INSTA-1407</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="G6" s="40" t="inlineStr">
         <is>
-          <t>DEF-SET-02</t>
+          <t>DEF-SET-02 / INSTA-1408</t>
         </is>
       </c>
     </row>
@@ -13940,12 +13940,12 @@
       </c>
       <c r="E96" s="58" t="inlineStr">
         <is>
-          <t>Product field opens but returns no options — the plan attached to this company has no products associated with it yet, so there is nothing to choose. (The field itself renders and is clickable.)</t>
+          <t>The Product field in the New Batch modal renders and opens, but returns no options: the plan attached to this test company has no products associated with it, so there is nothing selectable. Not a product defect — a data condition of the self-created test fixture. Exercising it would require associating products with a live plan.</t>
         </is>
       </c>
       <c r="F96" s="40" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="G96" s="40" t="inlineStr">
@@ -14195,7 +14195,17 @@
       </c>
       <c r="E105" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The company's Products grid displays (0 row(s)).</t>
+        </is>
+      </c>
+      <c r="F105" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G105" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14225,17 @@
       </c>
       <c r="E106" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Filter Products' opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F106" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G106" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14236,7 +14256,17 @@
       </c>
       <c r="E107" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists the product columns: ['Product Barcode', 'Product Name', 'Device Categories', 'Shares', 'Responsible Claim Payer', 'Bypass Pincode Scanning', 'Bypass Device Screen Photo', 'Bypass Screen Test', 'Bypass IMEI or Serial Number', 'Product Review', 'Plan', 'Remaining Pins', 'Average Rating', '5 Star', '4 Star', '3 Star', '2 Star', '1 Star', 'Status']</t>
+        </is>
+      </c>
+      <c r="F107" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G107" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14287,17 @@
       </c>
       <c r="E108" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected filter column 'Product Barcode'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F108" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G108" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14278,7 +14318,17 @@
       </c>
       <c r="E109" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The dependent value dropdown returns no options because the company product grid is empty at the time of the check — the test product created for this run was removed during teardown. The filter mechanism itself is verified working on populated product grids elsewhere in this run (e.g. Product Category &gt; Products returned Product Barcode values). Re-testing here would mean adding another product to a company that cannot be deleted (see DEF-SET-09).</t>
+        </is>
+      </c>
+      <c r="F109" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G109" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14350,17 @@
       </c>
       <c r="E110" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No value can be selected because the dependent dropdown is empty (see Company|5).</t>
+        </is>
+      </c>
+      <c r="F110" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G110" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14380,17 @@
       </c>
       <c r="E111" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the products grid (clicked).</t>
+        </is>
+      </c>
+      <c r="F111" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G111" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14410,17 @@
       </c>
       <c r="E112" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Products search accepts input and filters the grid.</t>
+        </is>
+      </c>
+      <c r="F112" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G112" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14440,17 @@
       </c>
       <c r="E113" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export control present; download not captured headless.</t>
+        </is>
+      </c>
+      <c r="F113" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G113" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14470,17 @@
       </c>
       <c r="E114" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t xml:space="preserve">New opens the New Product modal: New Product | close | Upload | file_upload | Product Barcode | Product Name * | Plan * | Device Categories * | Product Category | Responsible Claim </t>
+        </is>
+      </c>
+      <c r="F114" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G114" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14500,17 @@
       </c>
       <c r="E115" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile image section exposes a file input (1).</t>
+        </is>
+      </c>
+      <c r="F115" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G115" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14530,17 @@
       </c>
       <c r="E116" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected image reflects — image accepted and preview rendered=True.</t>
+        </is>
+      </c>
+      <c r="F116" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G116" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14560,17 @@
       </c>
       <c r="E117" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product barcode accepts input — {'label': 'Product Barcode', 'val': 'REGTESTBC0817'}.</t>
+        </is>
+      </c>
+      <c r="F117" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G117" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14590,17 @@
       </c>
       <c r="E118" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product name accepts input — {'label': 'Product Name *', 'val': 'RegressionTest0817'}.</t>
+        </is>
+      </c>
+      <c r="F118" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G118" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14621,17 @@
       </c>
       <c r="E119" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan field (#plan) opens a dropdown; options: ['2 - Years Warranty Replacement']</t>
+        </is>
+      </c>
+      <c r="F119" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G119" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14501,7 +14651,17 @@
       </c>
       <c r="E120" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected plan '2 - Years Warranty Replacement' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F120" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G120" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14522,7 +14682,17 @@
       </c>
       <c r="E121" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device Categories field opens a dropdown; options: ['Chromebook', 'Headphones / Earbuds', 'Laptop', 'Router', 'SmartPhone', 'SmartWatch', 'ta', 'Tablet']. (It is a multi-select: the option menu populates on keyboard focus/ArrowDown.)</t>
+        </is>
+      </c>
+      <c r="F121" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G121" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14712,17 @@
       </c>
       <c r="E122" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected device category 'Chromebook' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F122" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G122" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14742,17 @@
       </c>
       <c r="E123" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product Category field opens; options: ['Cables', 'Camera Lens', 'Case', 'Chargers', 'Power Banks', 'Screen Protectors', 'Smart Tag', 'Tempered Glass']</t>
+        </is>
+      </c>
+      <c r="F123" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G123" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14582,7 +14772,17 @@
       </c>
       <c r="E124" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected product category 'Cables' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F124" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G124" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14802,17 @@
       </c>
       <c r="E125" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Agreement accepts input — #agreement now reads 'Regression test agreement 2026-08-17'.</t>
+        </is>
+      </c>
+      <c r="F125" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G125" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14622,7 +14832,17 @@
       </c>
       <c r="E126" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>A workflow-to-bypass option can be selected — {'label': 'Bypass Screen Test', 'checked': True}.</t>
+        </is>
+      </c>
+      <c r="F126" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G126" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14863,17 @@
       </c>
       <c r="E127" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue ('checkSave &amp; Continue') closes the New Product modal and creates the product.</t>
+        </is>
+      </c>
+      <c r="F127" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G127" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14893,17 @@
       </c>
       <c r="E128" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>A product record opens from the company's products grid (ok; 1 product row(s)); its tabs are ['Details', 'Batches', 'Review Questions', 'Shares', 'Shop Setup', 'Orders', 'Timeline', 'Notes'].</t>
+        </is>
+      </c>
+      <c r="F128" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G128" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14923,17 @@
       </c>
       <c r="E129" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product details are displayed on the record — ['Product Barcode', 'Product Name', 'Plan', 'Device Categories', 'Agreement', 'Workflow'].</t>
+        </is>
+      </c>
+      <c r="F129" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G129" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14703,7 +14953,17 @@
       </c>
       <c r="E130" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Batches tab on the product record routes to its panel (True); tabs ['Details', 'Batches', 'Review Questions', 'Shares', 'Shop Setup', 'Orders', 'Timeline', 'Notes'].</t>
+        </is>
+      </c>
+      <c r="F130" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G130" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14723,7 +14983,17 @@
       </c>
       <c r="E131" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Batches containing this product are listed (0 row(s)): file_download | Export as CSV | All Batches | Custom Filter | arrow_drop_down | Filter Batches | No Records Found! | Bat</t>
+        </is>
+      </c>
+      <c r="F131" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G131" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14743,7 +15013,17 @@
       </c>
       <c r="E132" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Review Questions tab routes to its panel (True).</t>
+        </is>
+      </c>
+      <c r="F132" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G132" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14763,7 +15043,17 @@
       </c>
       <c r="E133" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add opens the review-questions picker: Add Review Question | close | check_box_outline_blank | 	 | Title | arrow_upward | 	 | Review Question | arrow_upward | 	Options |  | check_bo</t>
+        </is>
+      </c>
+      <c r="F133" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G133" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14784,7 +15074,17 @@
       </c>
       <c r="E134" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Review questions can be selected (checked).</t>
+        </is>
+      </c>
+      <c r="F134" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G134" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14805,7 +15105,17 @@
       </c>
       <c r="E135" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Add selected' ('checkAdd Selected') closes the picker and attaches the questions.</t>
+        </is>
+      </c>
+      <c r="F135" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G135" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14826,7 +15136,17 @@
       </c>
       <c r="E136" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Shop Set-up tab routes to its panel (True).</t>
+        </is>
+      </c>
+      <c r="F136" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G136" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14849,7 +15169,17 @@
       </c>
       <c r="E137" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Order Flow section displayed with its options (['Order flow', 'Claim', 'Registration']).</t>
+        </is>
+      </c>
+      <c r="F137" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G137" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14869,7 +15199,17 @@
       </c>
       <c r="E138" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>An order flow can be selected — {'label': 'Claim', 'checked': True}. Selecting it reveals the Flow configuration and Associated Products sections.</t>
+        </is>
+      </c>
+      <c r="F138" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G138" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14889,7 +15229,17 @@
       </c>
       <c r="E139" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Select All Devices' can be checked — {'label': 'Select All Devices', 'checked': True}.</t>
+        </is>
+      </c>
+      <c r="F139" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G139" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14909,7 +15259,17 @@
       </c>
       <c r="E140" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>With 'Select All Devices' unchecked ({'label': 'Select All Devices', 'checked': False}) the Device List becomes selectable — options ['3Plus Cruz', '3Plus Vibe', '3Plus Vibe Lite', '3Plus Vibe Pro', 'Accent FAST7 3G', 'Accent Pearl A4'], selected '3Plus Cruz'.</t>
+        </is>
+      </c>
+      <c r="F140" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G140" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14931,7 +15291,17 @@
       </c>
       <c r="E141" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Associated Products section displayed (True).</t>
+        </is>
+      </c>
+      <c r="F141" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G141" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14951,7 +15321,17 @@
       </c>
       <c r="E142" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product Category field in Associated Products opens (react-md select); options: ['Cables', 'Camera Lens', 'Case', 'Chargers', 'Power Banks', 'Screen Protectors', 'Smart Tag', 'Tempered Glass']</t>
+        </is>
+      </c>
+      <c r="F142" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G142" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14971,7 +15351,17 @@
       </c>
       <c r="E143" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected product category 'Cables' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F143" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G143" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14993,7 +15383,17 @@
       </c>
       <c r="E144" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The Associated Products "Products *" field (#order_products) returns no options for any Product Category tried (Cables, Case, Chargers, Screen Protectors, Tempered Glass). The list appears to be scoped to other products belonging to this company, and the test company has only the single product being configured — so there is nothing available to associate. Could not be exercised without adding further products to live configuration. Worth PM confirmation that the list is company-scoped.</t>
+        </is>
+      </c>
+      <c r="F144" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G144" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15013,7 +15413,17 @@
       </c>
       <c r="E145" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>The "Add a Product" control is present and clickable in the Associated Products section, but no product could be selected to add (see Company|40), so the add action was not exercised.</t>
+        </is>
+      </c>
+      <c r="F145" s="40" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="G145" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15443,17 @@
       </c>
       <c r="E146" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Remove control removes an associated product ('removeRemove').</t>
+        </is>
+      </c>
+      <c r="F146" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G146" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15053,7 +15473,17 @@
       </c>
       <c r="E147" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product order details section displayed — ['Original Price', 'Discount Type', 'Discount Value', 'Discounted Price', 'Shipping and Handling', 'Maximum Order Quantity'].</t>
+        </is>
+      </c>
+      <c r="F147" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G147" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15503,17 @@
       </c>
       <c r="E148" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Original price accepts input — #order_price now reads 'USD  1.00'.</t>
+        </is>
+      </c>
+      <c r="F148" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G148" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15533,17 @@
       </c>
       <c r="E149" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Discount Type field opens (react-md select); options: ['Fix', 'Percentage']</t>
+        </is>
+      </c>
+      <c r="F149" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G149" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15563,17 @@
       </c>
       <c r="E150" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected discount type 'Fix' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F150" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G150" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15133,7 +15593,17 @@
       </c>
       <c r="E151" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Discount value accepts input — #discount_value now reads '10'.</t>
+        </is>
+      </c>
+      <c r="F151" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G151" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15153,7 +15623,17 @@
       </c>
       <c r="E152" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Shipping and handling accepts input — #order_shipping_fee now reads 'USD  0.05'.</t>
+        </is>
+      </c>
+      <c r="F152" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G152" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15173,7 +15653,17 @@
       </c>
       <c r="E153" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Maximum order quantity accepts input — #order_maximum_quantity now reads '3'.</t>
+        </is>
+      </c>
+      <c r="F153" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G153" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15683,17 @@
       </c>
       <c r="E154" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product description rich-text editor (Quill) accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F154" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G154" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15713,17 @@
       </c>
       <c r="E155" s="40" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save ('checkSave and Close') stores the shop set-up configuration.</t>
+        </is>
+      </c>
+      <c r="F155" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G155" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15246,7 +15756,17 @@
       </c>
       <c r="E157" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline filter control opens the filter panel.</t>
+        </is>
+      </c>
+      <c r="F157" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G157" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15796,17 @@
       </c>
       <c r="E158" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter-field dropdown lists timeline columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F158" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G158" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15827,17 @@
       </c>
       <c r="E159" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; 'Select a value' appears.</t>
+        </is>
+      </c>
+      <c r="F159" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G159" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15318,7 +15858,17 @@
       </c>
       <c r="E160" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Dependent value dropdown for 'Action': ['Create Company', 'Update Company']</t>
+        </is>
+      </c>
+      <c r="F160" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G160" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15340,7 +15890,17 @@
       </c>
       <c r="E161" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected value 'Create Company' reflects on the field.</t>
+        </is>
+      </c>
+      <c r="F161" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G161" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15920,17 @@
       </c>
       <c r="E162" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applies to the timeline (clicked).</t>
+        </is>
+      </c>
+      <c r="F162" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G162" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15950,17 @@
       </c>
       <c r="E163" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline search accepts input and filters the activity list.</t>
+        </is>
+      </c>
+      <c r="F163" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G163" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15980,17 @@
       </c>
       <c r="E164" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline records the actions performed on this record — entries: ['Create']. Feed: keyboard_arrow_left | keyboard_arrow_right | All Activity | Custom Filter | Custom Filter | Custom Filter | Custom Filter | Custom Filter | Custom Fil</t>
+        </is>
+      </c>
+      <c r="F164" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G164" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15433,7 +16023,17 @@
       </c>
       <c r="E166" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens the note modal: New Note | close | Title * | &lt;&gt; |  |  |  |  | close | Cancel | check | Save &amp; Close</t>
+        </is>
+      </c>
+      <c r="F166" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G166" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15453,7 +16053,17 @@
       </c>
       <c r="E167" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F167" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G167" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15473,7 +16083,17 @@
       </c>
       <c r="E168" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Message/content rich-text box accepts input (True).</t>
+        </is>
+      </c>
+      <c r="F168" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G168" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15494,7 +16114,17 @@
       </c>
       <c r="E169" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close') closes the modal and the note appears in the list (found=True).</t>
+        </is>
+      </c>
+      <c r="F169" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G169" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15515,7 +16145,17 @@
       </c>
       <c r="E170" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit (clicked) opens the note modal populated — title reads 'RegressionTest Note Aug17'.</t>
+        </is>
+      </c>
+      <c r="F170" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G170" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15536,7 +16176,17 @@
       </c>
       <c r="E171" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Change reflects in the title field (True).</t>
+        </is>
+      </c>
+      <c r="F171" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G171" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15557,7 +16207,17 @@
       </c>
       <c r="E172" s="58" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close ('checkSave &amp; Close'); record reopened and the edited note persists (found=True).</t>
+        </is>
+      </c>
+      <c r="F172" s="40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G172" s="40" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15900,7 +16560,7 @@
       </c>
       <c r="G5" s="40" t="inlineStr">
         <is>
-          <t>DEF-SET-01</t>
+          <t>DEF-SET-01 / INSTA-1401</t>
         </is>
       </c>
     </row>
@@ -23492,7 +24152,7 @@
       </c>
       <c r="L1" s="50" t="inlineStr">
         <is>
-          <t>Resolution / notes</t>
+          <t>Jira issue</t>
         </is>
       </c>
       <c r="M1" s="50" t="inlineStr">
@@ -23504,17 +24164,17 @@
     <row r="2" ht="23.25" customHeight="1" s="41">
       <c r="A2" s="74" t="inlineStr">
         <is>
-          <t>DEF-001</t>
+          <t>DEF-SET-01</t>
         </is>
       </c>
       <c r="B2" s="74" t="inlineStr">
         <is>
-          <t>PORTAL - REGISTRATION / 12</t>
+          <t>SETTINGS - LANGUAGE / Grid|4</t>
         </is>
       </c>
       <c r="C2" s="74" t="inlineStr">
         <is>
-          <t>Product Barcode not shown on registration grid</t>
+          <t>Selecting any filter column on the Languages settings grid crashes the page to a blank screen</t>
         </is>
       </c>
       <c r="D2" s="74" t="inlineStr">
@@ -23534,285 +24194,1105 @@
       </c>
       <c r="G2" s="74" t="inlineStr">
         <is>
-          <t>1. Open Registration grid 2. Check Product Barcode column</t>
+          <t>1. Log in and go to Settings &gt; Languages. 2. Click 'Filter Languages'. 3. Open 'Select a filter' and choose any column (Language, ISO Code, Date Format or Time Format). RESULT: the app throws 'TypeError: array[key].filter is not a function at SelectFilter.mapArrayValues' (uncaught at GetLanguageFilter) and the entire page renders blank (document body length 0, no controls); a reload is required. Reproduced on all four filter columns. The identical interaction on other settings grids (e.g. Coverage Types) works normally.</t>
         </is>
       </c>
       <c r="H2" s="74" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
         </is>
       </c>
       <c r="I2" s="74" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
         </is>
       </c>
       <c r="J2" s="74" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="K2" s="74" t="n"/>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K2" s="74" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
       <c r="L2" s="74" t="inlineStr">
         <is>
-          <t>Under investigation</t>
+          <t>INSTA-1401</t>
         </is>
       </c>
       <c r="M2" s="74" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" s="41">
-      <c r="A3" s="51" t="n"/>
-      <c r="B3" s="51" t="n"/>
-      <c r="C3" s="51" t="n"/>
-      <c r="D3" s="51" t="n"/>
-      <c r="E3" s="51" t="n"/>
-      <c r="F3" s="51" t="n"/>
-      <c r="G3" s="51" t="n"/>
-      <c r="H3" s="51" t="n"/>
-      <c r="I3" s="51" t="n"/>
-      <c r="J3" s="51" t="n"/>
-      <c r="K3" s="51" t="n"/>
-      <c r="L3" s="51" t="n"/>
+      <c r="A3" s="51" t="inlineStr">
+        <is>
+          <t>DEF-SET-09</t>
+        </is>
+      </c>
+      <c r="B3" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - COMPANY / record + Plans sub-grid</t>
+        </is>
+      </c>
+      <c r="C3" s="51" t="inlineStr">
+        <is>
+          <t>Deleting a company and removing a plan from a company both fail with HTTP 400 and no error is shown to the user</t>
+        </is>
+      </c>
+      <c r="D3" s="51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E3" s="51" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F3" s="51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G3" s="51" t="inlineStr">
+        <is>
+          <t>1. Settings &gt; Company &gt; open a company record. 2. Click Delete and confirm Yes. RESULT: DELETE /company/&lt;id&gt; returns HTTP 400, the confirmation dialog stays open, no error message is surfaced, and the company remains in the grid. 3. Same on the company's Plans tab: click remove on a plan row and confirm Yes. RESULT: DELETE /company_plan/&lt;id&gt; returns HTTP 400, the plan stays attached, no error is surfaced. The user is given no indication the operation failed.</t>
+        </is>
+      </c>
+      <c r="H3" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I3" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J3" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K3" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L3" s="51" t="inlineStr">
+        <is>
+          <t>INSTA-1402</t>
+        </is>
+      </c>
       <c r="M3" s="51" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="41">
-      <c r="A4" s="51" t="n"/>
-      <c r="B4" s="51" t="n"/>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="51" t="n"/>
-      <c r="E4" s="51" t="n"/>
-      <c r="F4" s="51" t="n"/>
-      <c r="G4" s="51" t="n"/>
-      <c r="H4" s="51" t="n"/>
-      <c r="I4" s="51" t="n"/>
-      <c r="J4" s="51" t="n"/>
-      <c r="K4" s="51" t="n"/>
-      <c r="L4" s="51" t="n"/>
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t>DEF-SET-10</t>
+        </is>
+      </c>
+      <c r="B4" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - COMPANY / record Status</t>
+        </is>
+      </c>
+      <c r="C4" s="51" t="inlineStr">
+        <is>
+          <t>Company record Status selector does not apply the chosen value — a company cannot be set Inactive</t>
+        </is>
+      </c>
+      <c r="D4" s="51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E4" s="51" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F4" s="51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G4" s="51" t="inlineStr">
+        <is>
+          <t>1. Settings &gt; Company &gt; open a company record. 2. Open the Status selector (react-md, #status-toggle) and choose 'Inactive'. RESULT: the hidden #status input still reads 'Active' — the selection never binds to form state. 3. Save. Save reports success with no validation errors, but reopening the record shows Status = Active. Combined with DEF-SET-09 this leaves no way to delete or deactivate a company.</t>
+        </is>
+      </c>
+      <c r="H4" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I4" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J4" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K4" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L4" s="51" t="inlineStr">
+        <is>
+          <t>INSTA-1403</t>
+        </is>
+      </c>
       <c r="M4" s="51" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="41">
-      <c r="A5" s="51" t="n"/>
-      <c r="B5" s="51" t="n"/>
-      <c r="C5" s="51" t="n"/>
-      <c r="D5" s="51" t="n"/>
-      <c r="E5" s="51" t="n"/>
-      <c r="F5" s="51" t="n"/>
-      <c r="G5" s="51" t="n"/>
-      <c r="H5" s="51" t="n"/>
-      <c r="I5" s="51" t="n"/>
-      <c r="J5" s="51" t="n"/>
-      <c r="K5" s="51" t="n"/>
-      <c r="L5" s="51" t="n"/>
+      <c r="A5" s="51" t="inlineStr">
+        <is>
+          <t>DEF-CLAIM-01</t>
+        </is>
+      </c>
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>CLAIM REPORTS / Repair Receipt|9</t>
+        </is>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>Covered amount field on the claim Repair Receipt tab rejects all input</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E5" s="51" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>1. Claim Reports &gt; open any claim &gt; Repair Receipt tab. 2. Tick 'Is the customer using an insurance?'. 3. Try to enter a value in the Covered amount field (#covered_amount). RESULT: the field stays at 'USD  0.00' under every input method (Playwright fill, select-all + retype, character-by-character typing). It is a plain text input with disabled=false, readOnly=false and no maxlength/pattern. The adjacent #repair_amount field, rendered identically, accepts input normally (typing 250 gives 'USD  2.50').</t>
+        </is>
+      </c>
+      <c r="H5" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I5" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J5" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K5" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L5" s="51" t="inlineStr">
+        <is>
+          <t>INSTA-1404</t>
+        </is>
+      </c>
       <c r="M5" s="51" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="41">
-      <c r="A6" s="51" t="n"/>
-      <c r="B6" s="51" t="n"/>
-      <c r="C6" s="51" t="n"/>
-      <c r="D6" s="51" t="n"/>
-      <c r="E6" s="51" t="n"/>
-      <c r="F6" s="51" t="n"/>
-      <c r="G6" s="51" t="n"/>
-      <c r="H6" s="51" t="n"/>
-      <c r="I6" s="51" t="n"/>
-      <c r="J6" s="51" t="n"/>
-      <c r="K6" s="51" t="n"/>
-      <c r="L6" s="51" t="n"/>
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>DEF-REG-01</t>
+        </is>
+      </c>
+      <c r="B6" s="51" t="inlineStr">
+        <is>
+          <t>PORTAL - REGISTRATION / Claim|5</t>
+        </is>
+      </c>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>New Claim wizard: the required Notes field is not enforced — the wizard advances with it empty</t>
+        </is>
+      </c>
+      <c r="D6" s="51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="51" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F6" s="51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G6" s="51" t="inlineStr">
+        <is>
+          <t>1. Registrations &gt; open a registration &gt; Claim tab &gt; New. 2. Advance to Step 2. 3. Leave the Notes field empty and click Next. RESULT: the wizard advances from Step 2 to Step 3 with no validation message, even though the field is labelled 'Notes *' and the textarea #notes carries required=true. Expected: the Notes field validates and blocks progression.</t>
+        </is>
+      </c>
+      <c r="H6" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I6" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J6" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K6" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L6" s="51" t="inlineStr">
+        <is>
+          <t>INSTA-1405</t>
+        </is>
+      </c>
       <c r="M6" s="51" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="41">
-      <c r="A7" s="51" t="n"/>
-      <c r="B7" s="51" t="n"/>
-      <c r="C7" s="51" t="n"/>
-      <c r="D7" s="51" t="n"/>
-      <c r="E7" s="51" t="n"/>
-      <c r="F7" s="51" t="n"/>
-      <c r="G7" s="51" t="n"/>
-      <c r="H7" s="51" t="n"/>
-      <c r="I7" s="51" t="n"/>
-      <c r="J7" s="51" t="n"/>
-      <c r="K7" s="51" t="n"/>
-      <c r="L7" s="51" t="n"/>
+      <c r="A7" s="51" t="inlineStr">
+        <is>
+          <t>DEF-SET-03</t>
+        </is>
+      </c>
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - DEVICE CATEGORY / Devices|13</t>
+        </is>
+      </c>
+      <c r="C7" s="51" t="inlineStr">
+        <is>
+          <t>Add Devices wizard: the Step 2 'Search Devices' field does not filter the list</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="51" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F7" s="51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G7" s="51" t="inlineStr">
+        <is>
+          <t>1. Settings &gt; Device Category &gt; open a category (e.g. Chromebook) &gt; Devices tab &gt; Add. 2. Select a brand and click Next. 3. Type into 'Search Devices...'. RESULT: the list never filters. Baseline 22 rows; searching '100e' -&gt; still 22 rows (first rows unchanged); '14e' -&gt; 22; a nonsense term 'zzzzz' -&gt; still 22 rows after 10s. The field accepts typing but no filtering is applied.</t>
+        </is>
+      </c>
+      <c r="H7" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I7" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J7" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K7" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L7" s="51" t="inlineStr">
+        <is>
+          <t>INSTA-1406</t>
+        </is>
+      </c>
       <c r="M7" s="51" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="41">
-      <c r="A8" s="51" t="n"/>
-      <c r="B8" s="51" t="n"/>
-      <c r="C8" s="51" t="n"/>
-      <c r="D8" s="51" t="n"/>
-      <c r="E8" s="51" t="n"/>
-      <c r="F8" s="51" t="n"/>
-      <c r="G8" s="51" t="n"/>
-      <c r="H8" s="51" t="n"/>
-      <c r="I8" s="51" t="n"/>
-      <c r="J8" s="51" t="n"/>
-      <c r="K8" s="51" t="n"/>
-      <c r="L8" s="51" t="n"/>
+      <c r="A8" s="51" t="inlineStr">
+        <is>
+          <t>DEF-SET-05</t>
+        </is>
+      </c>
+      <c r="B8" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - PRODUCT CATEGORY / Timeline|8</t>
+        </is>
+      </c>
+      <c r="C8" s="51" t="inlineStr">
+        <is>
+          <t>Product Category records write no timeline entries</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="51" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F8" s="51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G8" s="51" t="inlineStr">
+        <is>
+          <t>1. Settings &gt; Product Category &gt; create a category. 2. Open it &gt; Timeline tab (ensure the 'All Activity' filter set is selected). RESULT: 'No Results Found!' — the creation is not logged. A long-standing real category (Cables) is likewise empty. By contrast the equivalent Device Category timeline does log activity (Create Category / Update Category plus historic entries), so timeline logging works elsewhere.</t>
+        </is>
+      </c>
+      <c r="H8" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I8" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J8" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K8" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L8" s="51" t="inlineStr">
+        <is>
+          <t>INSTA-1407</t>
+        </is>
+      </c>
       <c r="M8" s="51" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="41">
-      <c r="A9" s="51" t="n"/>
-      <c r="B9" s="51" t="n"/>
-      <c r="C9" s="51" t="n"/>
-      <c r="D9" s="51" t="n"/>
-      <c r="E9" s="51" t="n"/>
-      <c r="F9" s="51" t="n"/>
-      <c r="G9" s="51" t="n"/>
-      <c r="H9" s="51" t="n"/>
-      <c r="I9" s="51" t="n"/>
-      <c r="J9" s="51" t="n"/>
-      <c r="K9" s="51" t="n"/>
-      <c r="L9" s="51" t="n"/>
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>DEF-SET-02</t>
+        </is>
+      </c>
+      <c r="B9" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - REPAIR NETWORK / Grid|5</t>
+        </is>
+      </c>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>Repair Network grid filter returns no selectable values</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E9" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F9" s="51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G9" s="51" t="inlineStr">
+        <is>
+          <t>1. Settings &gt; Repair Network. 2. Click 'Filter Repair Network' and choose the only column offered, 'Repair Network Name'. RESULT: the dependent 'Select a value' dropdown is empty even though the grid holds a record ('TRG'). No JavaScript error is raised and the page stays usable. Expected: the value list is populated from the selected column.</t>
+        </is>
+      </c>
+      <c r="H9" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I9" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J9" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K9" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L9" s="51" t="inlineStr">
+        <is>
+          <t>INSTA-1408</t>
+        </is>
+      </c>
       <c r="M9" s="51" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="41">
-      <c r="A10" s="51" t="n"/>
-      <c r="B10" s="51" t="n"/>
-      <c r="C10" s="51" t="n"/>
-      <c r="D10" s="51" t="n"/>
-      <c r="E10" s="51" t="n"/>
-      <c r="F10" s="51" t="n"/>
-      <c r="G10" s="51" t="n"/>
-      <c r="H10" s="51" t="n"/>
-      <c r="I10" s="51" t="n"/>
-      <c r="J10" s="51" t="n"/>
-      <c r="K10" s="51" t="n"/>
-      <c r="L10" s="51" t="n"/>
+      <c r="A10" s="51" t="inlineStr">
+        <is>
+          <t>DEF-USERS-01</t>
+        </is>
+      </c>
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t>USERS / New User|12</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>New User country list does not match spec — Japan, Mexico and Spain missing, Puerto Rico extra</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E10" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F10" s="51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G10" s="51" t="inlineStr">
+        <is>
+          <t>1. Users &gt; New. 2. Set Role = Basic Client (the role that exposes customer contact fields). 3. Open the Country dropdown. RESULT: it lists Canada, Puerto Rico, United Kingdom, United States (4). Expected per the test case: Canada, Japan, Mexico, Spain, United Kingdom, United States (6). The list is also inconsistent with the Country Code dropdown, which still offers JP (+81) and MX (+52) for countries that cannot be selected.</t>
+        </is>
+      </c>
+      <c r="H10" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I10" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J10" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K10" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L10" s="51" t="inlineStr">
+        <is>
+          <t>INSTA-1409</t>
+        </is>
+      </c>
       <c r="M10" s="51" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="41">
-      <c r="A11" s="51" t="n"/>
-      <c r="B11" s="51" t="n"/>
-      <c r="C11" s="51" t="n"/>
-      <c r="D11" s="51" t="n"/>
-      <c r="E11" s="51" t="n"/>
-      <c r="F11" s="51" t="n"/>
-      <c r="G11" s="51" t="n"/>
-      <c r="H11" s="51" t="n"/>
-      <c r="I11" s="51" t="n"/>
-      <c r="J11" s="51" t="n"/>
-      <c r="K11" s="51" t="n"/>
-      <c r="L11" s="51" t="n"/>
+      <c r="A11" s="51" t="inlineStr">
+        <is>
+          <t>DEV-REG-01</t>
+        </is>
+      </c>
+      <c r="B11" s="51" t="inlineStr">
+        <is>
+          <t>PORTAL - REGISTRATION / Details|6-7</t>
+        </is>
+      </c>
+      <c r="C11" s="51" t="inlineStr">
+        <is>
+          <t>No replace-file control for a registration's store receipt</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E11" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F11" s="51" t="inlineStr">
+        <is>
+          <t>For PM confirmation</t>
+        </is>
+      </c>
+      <c r="G11" s="51" t="inlineStr">
+        <is>
+          <t>The Store Receipt section offers only view actions (View Receipt / View Image / View Photo); input[type=file] count is 0 in both the Details tab and the View Receipt modal. The test case expects a replace-file button opening the OS file explorer. Likely test-case drift — for PM confirmation.</t>
+        </is>
+      </c>
+      <c r="H11" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I11" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J11" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K11" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L11" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M11" s="51" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="41">
-      <c r="A12" s="51" t="n"/>
-      <c r="B12" s="51" t="n"/>
-      <c r="C12" s="51" t="n"/>
-      <c r="D12" s="51" t="n"/>
-      <c r="E12" s="51" t="n"/>
-      <c r="F12" s="51" t="n"/>
-      <c r="G12" s="51" t="n"/>
-      <c r="H12" s="51" t="n"/>
-      <c r="I12" s="51" t="n"/>
-      <c r="J12" s="51" t="n"/>
-      <c r="K12" s="51" t="n"/>
-      <c r="L12" s="51" t="n"/>
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>DEV-CLAIM-01</t>
+        </is>
+      </c>
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>CLAIM REPORTS / Record|7-8</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>Claim record has no 'Claim Summary' or 'Claim Status Details' tab</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E12" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F12" s="51" t="inlineStr">
+        <is>
+          <t>For PM confirmation</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>Tabs present: Registration, Customer Details, Location, Appointment, Claim Receipt, Repair Receipt, Repair Approval, Reimbursement Review, Payment Info, Timeline, Notes. The two tabs the test cases expect are absent and five undocumented tabs are present. Looks like a claim redesign — for PM confirmation.</t>
+        </is>
+      </c>
+      <c r="H12" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I12" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J12" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K12" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L12" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M12" s="51" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="41">
-      <c r="A13" s="51" t="n"/>
-      <c r="B13" s="51" t="n"/>
-      <c r="C13" s="51" t="n"/>
-      <c r="D13" s="51" t="n"/>
-      <c r="E13" s="51" t="n"/>
-      <c r="F13" s="51" t="n"/>
-      <c r="G13" s="51" t="n"/>
-      <c r="H13" s="51" t="n"/>
-      <c r="I13" s="51" t="n"/>
-      <c r="J13" s="51" t="n"/>
-      <c r="K13" s="51" t="n"/>
-      <c r="L13" s="51" t="n"/>
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>DEV-CLAIM-02</t>
+        </is>
+      </c>
+      <c r="B13" s="51" t="inlineStr">
+        <is>
+          <t>CLAIM REPORTS / Claim Reports|11-12</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="inlineStr">
+        <is>
+          <t>New Claim wizard Step 4 is 'Claim Receipt', not the 'Problem Summary' the test cases describe</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E13" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>For PM confirmation</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>Step 4 renders an InstaProtek Product Guarantee Claim summary (Claim Number, Policy Number, Customer Information, Coverage Information, Shipping/Order Details) and is read-only. No Problem Date / Problem Summary fields exist anywhere in the flow. Matches the redesign noted on the QA environment in the previous cycle — for PM confirmation.</t>
+        </is>
+      </c>
+      <c r="H13" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I13" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J13" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K13" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L13" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M13" s="51" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="41">
-      <c r="A14" s="51" t="n"/>
-      <c r="B14" s="51" t="n"/>
-      <c r="C14" s="51" t="n"/>
-      <c r="D14" s="51" t="n"/>
-      <c r="E14" s="51" t="n"/>
-      <c r="F14" s="51" t="n"/>
-      <c r="G14" s="51" t="n"/>
-      <c r="H14" s="51" t="n"/>
-      <c r="I14" s="51" t="n"/>
-      <c r="J14" s="51" t="n"/>
-      <c r="K14" s="51" t="n"/>
-      <c r="L14" s="51" t="n"/>
+      <c r="A14" s="51" t="inlineStr">
+        <is>
+          <t>DEV-SET-01</t>
+        </is>
+      </c>
+      <c r="B14" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - PRODUCT CATEGORY / Products|9-12</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>Product Category record has no control to add products</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="51" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>For PM confirmation</t>
+        </is>
+      </c>
+      <c r="G14" s="51" t="inlineStr">
+        <is>
+          <t>The Products tab of a Product Category record exposes only 'Export as CSV' and 'Filter Products' — no add/New control in any of the categories checked (the new test category plus real categories Cables 27 products, Camera Lens 20, Case 24). Products do carry a Product Category field on the company product form, so association may be intended from the product side only — for PM confirmation.</t>
+        </is>
+      </c>
+      <c r="H14" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I14" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J14" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K14" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L14" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M14" s="51" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="41">
-      <c r="A15" s="51" t="n"/>
-      <c r="B15" s="51" t="n"/>
-      <c r="C15" s="51" t="n"/>
-      <c r="D15" s="51" t="n"/>
-      <c r="E15" s="51" t="n"/>
-      <c r="F15" s="51" t="n"/>
-      <c r="G15" s="51" t="n"/>
-      <c r="H15" s="51" t="n"/>
-      <c r="I15" s="51" t="n"/>
-      <c r="J15" s="51" t="n"/>
-      <c r="K15" s="51" t="n"/>
-      <c r="L15" s="51" t="n"/>
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>DEV-SET-02</t>
+        </is>
+      </c>
+      <c r="B15" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - PLAN / New Plan|5-7</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="inlineStr">
+        <is>
+          <t>New Plan form has no 'Plan Type' field</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E15" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>For PM confirmation</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>Step 1 renders exactly: Plan Name*, Region*, Coverage Amount*, SKU, Administrator*, Underwriter*, Coverage Type*, Coverage Cost Type*, Coverage Period (Year/s)*, Coverage Type Amount*, Channel* plus the image upload. The words 'Single'/'Multiple' appear nowhere. The test cases expect a Plan Type defaulting to Single — for PM confirmation.</t>
+        </is>
+      </c>
+      <c r="H15" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I15" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J15" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K15" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L15" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M15" s="51" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="41">
-      <c r="A16" s="51" t="n"/>
-      <c r="B16" s="51" t="n"/>
-      <c r="C16" s="51" t="n"/>
-      <c r="D16" s="51" t="n"/>
-      <c r="E16" s="51" t="n"/>
-      <c r="F16" s="51" t="n"/>
-      <c r="G16" s="51" t="n"/>
-      <c r="H16" s="51" t="n"/>
-      <c r="I16" s="51" t="n"/>
-      <c r="J16" s="51" t="n"/>
-      <c r="K16" s="51" t="n"/>
-      <c r="L16" s="51" t="n"/>
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>DEV-SET-03</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - COMPANY / Details|7-8</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>No 'Device Management System' field on the company Details form</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
+          <t>For PM confirmation</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="inlineStr">
+        <is>
+          <t>After enabling the Enterprise Program the only dropdowns are Repair Network, Country and Country Code. A Device Management System selector does exist, but on the plan Batch modal (#integrated_company) rather than company Details — the field appears to have moved. For PM confirmation.</t>
+        </is>
+      </c>
+      <c r="H16" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I16" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J16" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K16" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L16" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M16" s="51" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="41">
-      <c r="A17" s="51" t="n"/>
-      <c r="B17" s="51" t="n"/>
-      <c r="C17" s="51" t="n"/>
-      <c r="D17" s="51" t="n"/>
-      <c r="E17" s="51" t="n"/>
-      <c r="F17" s="51" t="n"/>
-      <c r="G17" s="51" t="n"/>
-      <c r="H17" s="51" t="n"/>
-      <c r="I17" s="51" t="n"/>
-      <c r="J17" s="51" t="n"/>
-      <c r="K17" s="51" t="n"/>
-      <c r="L17" s="51" t="n"/>
+      <c r="A17" s="51" t="inlineStr">
+        <is>
+          <t>DEV-SET-04</t>
+        </is>
+      </c>
+      <c r="B17" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - COMPANY / Users|10</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>No resend-invite action on the company users grid</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E17" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F17" s="51" t="inlineStr">
+        <is>
+          <t>For PM confirmation</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="inlineStr">
+        <is>
+          <t>A populated company (C2 Wireless, 1 user) exposes only edit / lock / remove_circle row actions. The test case expects a resend-invite action. For PM confirmation.</t>
+        </is>
+      </c>
+      <c r="H17" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I17" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J17" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K17" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L17" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M17" s="51" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="41">
-      <c r="A18" s="51" t="n"/>
-      <c r="B18" s="51" t="n"/>
-      <c r="C18" s="51" t="n"/>
-      <c r="D18" s="51" t="n"/>
-      <c r="E18" s="51" t="n"/>
-      <c r="F18" s="51" t="n"/>
-      <c r="G18" s="51" t="n"/>
-      <c r="H18" s="51" t="n"/>
-      <c r="I18" s="51" t="n"/>
-      <c r="J18" s="51" t="n"/>
-      <c r="K18" s="51" t="n"/>
-      <c r="L18" s="51" t="n"/>
+      <c r="A18" s="51" t="inlineStr">
+        <is>
+          <t>DEV-SET-05</t>
+        </is>
+      </c>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>SETTINGS - COMPANY / Plans|11</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>No image upload in the company's Add New Plan modal</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E18" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F18" s="51" t="inlineStr">
+        <is>
+          <t>For PM confirmation</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="inlineStr">
+        <is>
+          <t>The company Add New Plan modal is a two-step plan picker (Step 1 lists existing plans, Step 2 captures the Plan Code) and contains 0 file inputs. The test case expects a profile image section. For PM confirmation.</t>
+        </is>
+      </c>
+      <c r="H18" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I18" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J18" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K18" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L18" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M18" s="51" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="41">
-      <c r="A19" s="51" t="n"/>
-      <c r="B19" s="51" t="n"/>
-      <c r="C19" s="51" t="n"/>
-      <c r="D19" s="51" t="n"/>
-      <c r="E19" s="51" t="n"/>
-      <c r="F19" s="51" t="n"/>
-      <c r="G19" s="51" t="n"/>
-      <c r="H19" s="51" t="n"/>
-      <c r="I19" s="51" t="n"/>
-      <c r="J19" s="51" t="n"/>
-      <c r="K19" s="51" t="n"/>
-      <c r="L19" s="51" t="n"/>
+      <c r="A19" s="51" t="inlineStr">
+        <is>
+          <t>OBS-SET-01</t>
+        </is>
+      </c>
+      <c r="B19" s="51" t="inlineStr">
+        <is>
+          <t>All grids / Add Filter scenarios</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>Saved 'Custom Filter' tabs created by Add Filter cannot be removed from the UI</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E19" s="51" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="inlineStr">
+        <is>
+          <t>Every execution of an 'Add Filter' scenario permanently adds a 'Custom Filter' tab to that grid for the logged-in user. The tabs are rendered as &lt;li class='dnaTable2-headerSet-item'&gt;&lt;a data-setindex=N&gt; with no close/remove affordance anywhere in the UI, so they accumulate (12+ observed on some grids) and cannot be cleaned up. Noted as run residue on the agentqa account.</t>
+        </is>
+      </c>
+      <c r="H19" s="51" t="inlineStr">
+        <is>
+          <t>Nullnet (crm.nullnet.instaprotek.com) — carries live production data</t>
+        </is>
+      </c>
+      <c r="I19" s="51" t="inlineStr">
+        <is>
+          <t>Automated regression run (agentqa@dnamicro.com)</t>
+        </is>
+      </c>
+      <c r="J19" s="51" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="K19" s="51" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="L19" s="51" t="inlineStr">
+        <is>
+          <t>not filed — reported for PM confirmation</t>
+        </is>
+      </c>
       <c r="M19" s="51" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="41">
@@ -25155,7 +26635,7 @@
       </c>
       <c r="G23" s="40" t="inlineStr">
         <is>
-          <t>DEF-USERS-01</t>
+          <t>DEF-USERS-01 / INSTA-1409</t>
         </is>
       </c>
     </row>
@@ -26659,7 +28139,7 @@
       </c>
       <c r="G31" s="40" t="inlineStr">
         <is>
-          <t>DEF-REG-01</t>
+          <t>DEF-REG-01 / INSTA-1405</t>
         </is>
       </c>
     </row>
@@ -35177,7 +36657,7 @@
       </c>
       <c r="G61" s="40" t="inlineStr">
         <is>
-          <t>DEF-CLAIM-01</t>
+          <t>DEF-CLAIM-01 / INSTA-1404</t>
         </is>
       </c>
     </row>
